--- a/data/research_roadmap_report.xlsx
+++ b/data/research_roadmap_report.xlsx
@@ -16,40 +16,41 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方向 3 · 乳酸-乳酰化对小 RNA 稳态的调控（你的身份标" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同时必须做的「减法」- What to drop" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经本项目核实过的锚点文献（PMID 已验证）- Verifie" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读顺序与时间安排 - Reading order and t" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读顺序与时间安排（粗排，已被 §13 取代）- Readin" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文 + English（双语表）" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文 + English（双语表） (2)" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文 (3)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xiaodong ZOU · 2026-09-28" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.2 科学前提" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.6 可行性：为什么是你" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2 科学前提 —— 以及一个必须正面处理的竞争解释" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 科学前提 —— 先例已经存在，而且是 RNA 酶" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五方向决策表 - Decision matrix" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.1 十二周总览 - Twelve-week overvi" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W1 · TDMD 机制奠基：谁识别、谁泛素化、谁被降解" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W2 · 机器的边界、保护面与结构约束" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W3 · 把「半衰期」变成可测量的数字" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W4 · AMPK 底物识别语法——决定我的位点预测可不可信" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W5 · 信号 × miRNA：既有证据与反向因果的威胁" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W6 · 代谢记忆：疾病叙事与已有机制解释" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W7 · 竞争风险周：miR-29 为什么被关掉——转录解释已" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W8 · 尿苷化机器：TUT4-7 与 DIS3L2 的完整通" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W9 · 落点器官：肠狭窄与心脏纤维化的真实病理" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W10 · 乳酰化：非组蛋白与 RNA 机器的既有先例" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W11 · 平台与编辑：方向 4-5 的可行性底座" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W12 · 收口：竞争监视 + 写出 Specific Aim" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English field reference" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 · 总技能矩阵 - Master skills matri" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A 激酶生化（Aim 1 的核心，也是你最大的技术缺口）" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B 细胞与代谢处理" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C RNA 稳定性（Aim 2 的核心）" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 · 方向 2：TUT4-7–miR-29 纤维化检查点" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 · 方向 3：乳酸-乳酰化 × 小 RNA 稳态" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 · 方向 4：类器官 TDMD 报告平台" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 · 方向 5：碱基编辑解剖 TDMD 功能语法" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 · 必须找合作者的四处（不要自己做）" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 · 学习顺序（与 12 周阅读计划对齐）" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文 (4)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xiaodong ZOU · 2026-09-28" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.2 科学前提" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.6 可行性：为什么是你" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2 科学前提 —— 以及一个必须正面处理的竞争解释" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 科学前提 —— 先例已经存在，而且是 RNA 酶" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五方向决策表 - Decision matrix" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.1 十二周总览 - Twelve-week overvi" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W1 · TDMD 机制奠基：谁识别、谁泛素化、谁被降解" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W2 · 机器的边界、保护面与结构约束" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W3 · 把「半衰期」变成可测量的数字" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W4 · AMPK 底物识别语法——决定我的位点预测可不可信" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W5 · 信号 × miRNA：既有证据与反向因果的威胁" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W6 · 代谢记忆：疾病叙事与已有机制解释" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W7 · 竞争风险周：miR-29 为什么被关掉——转录解释已" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W8 · 尿苷化机器：TUT4-7 与 DIS3L2 的完整通" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W9 · 落点器官：肠狭窄与心脏纤维化的真实病理" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W10 · 乳酰化：非组蛋白与 RNA 机器的既有先例" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W11 · 平台与编辑：方向 4-5 的可行性底座" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W12 · 收口：竞争监视 + 写出 Specific Aim" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English field reference" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 · 总技能矩阵 - Master skills matri" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A 激酶生化（Aim 1 的核心，也是你最大的技术缺口）" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B 细胞与代谢处理" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C RNA 稳定性（Aim 2 的核心）" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 · 方向 2：TUT4-7–miR-29 纤维化检查点" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 · 方向 3：乳酸-乳酰化 × 小 RNA 稳态" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 · 方向 4：类器官 TDMD 报告平台" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 · 方向 5：碱基编辑解剖 TDMD 功能语法" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 · 必须找合作者的四处（不要自己做）" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 · 学习顺序（与 12 周阅读计划对齐）" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B344"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -553,14 +554,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1 · 研究分类 / Research Classification</t>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29 更新（本次并入 68 篇全文笔记的结果） 阅读计划那 68 篇的笔记已按全文填完（43 篇开放全文 + 22 篇你下载的 PDF + 3 篇替代文献），读全文带来的改动已经并进正文，不只是附在末尾： · §12 方向 1 新增 P2b（机器判别的定量尺度：trigger 偏好 up to 70 倍；加侧翼后 3 nM vs 300 nM）与 P8（⚠️ ZSWIM8 同源物 EBAX-1 有非 TDMD 功能 → KO 表型不能直接归因于 TDMD）； · §12 方向 2 的竞争解释 P3 被量化（28%／46%／37%；Smad3 位点在上游 22 kb），新增 P6（三成员丰度差 5–14 倍），Aim 1 因此有了定量门槛而不只是方向性判断； · §13 的 W6/W7/W9 三篇换成可取全文的替代文献并明示为 T2 降级；分层时间预算按实际层级重算为 39.5 小时（原写 33 小时，与它自己给出的每篇时长 26×60+28×25+14×10=40 h 不符，已改为按实际层级计算的值）； · §10 关闭「四栏待核对」这一缺口，并列出读全文后新暴露的三处缺口（A 丰度不对称、B 归因约束、C 代谢记忆证据器官偏差）。</t>
         </is>
       </c>
     </row>
@@ -572,15 +569,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>1 · 研究分类 / Research Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>按 CV 17 篇 + 9 项基金，你做过的研究可归为 6 个方向。编号沿用 CV 中的论文序号。</t>
         </is>
       </c>
     </row>
@@ -588,7 +589,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>发表结构的三句话概括：</t>
+          <t>按 CV 17 篇 + 9 项基金，你做过的研究可归为 6 个方向。编号沿用 CV 中的论文序号。</t>
         </is>
       </c>
     </row>
@@ -596,7 +597,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>· 你的 7 篇一作全部压在 B+C+D+A 上（代谢、纤维化、大动物模型），不在你现在所处的 F（小 RNA）。</t>
+          <t>发表结构的三句话概括：</t>
         </is>
       </c>
     </row>
@@ -604,7 +605,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>· 你的 3 篇末位作者全是书章节——它证明方法可信度，不构成「我有通讯作者原创论文」。</t>
+          <t>· 你的 7 篇一作全部压在 B+C+D+A 上（代谢、纤维化、大动物模型），不在你现在所处的 F（小 RNA）。</t>
         </is>
       </c>
     </row>
@@ -612,27 +613,27 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>· 你的 3 篇末位作者全是书章节——它证明方法可信度，不构成「我有通讯作者原创论文」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>· 你在 MSKCC 一年多，F 方向零一作。这是当前最大的结构性短板。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>English</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>From the 17 publications and 9 funded projects on the CV, the prior work sorts into six directions (see the bilingual table above; CV numbering retained).</t>
         </is>
       </c>
     </row>
@@ -640,47 +641,47 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>From the 17 publications and 9 funded projects on the CV, the prior work sorts into six directions (see the bilingual table above; CV numbering retained).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Three-sentence summary of the publication structure: (1) all 7 first-author papers sit in directions B+C+D+A — metabolism, fibrosis, large-animal models — none in F, the small-RNA field you currently work in; (2) the 3 last-author items are all book chapters (*Methods Mol Biol*), which evidence methodological credibility but do not constitute corresponding-author original research; (3) after more than a year at MSKCC there is no first-author output in F — the single largest structural weakness right now.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2 · 逐方向文献综述 / Literature Review by Direction</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>依据说明： 本节的「进展/热点/空白/趋势」出自我对这些领域的知识，不是从你的资料推出的，也不引用具体论文标题以免编造。第 6 节另附一张经本项目核实过 PMID 的锚点文献表。不确定处我会明说。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A · 大动物基因编辑与疾病模型</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -688,7 +689,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>· 进展： CRISPR/Cas9 + 体细胞核移植（SCNT）在猪上已是成熟流水线；从单基因敲除走向精准敲入、碱基编辑（ABE/CBE）、prime editing。多位点编辑猪（去除免疫原/PERV）已推动猪心、猪肾移植进入人体实质阶段（2022 年以来）。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -696,7 +697,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>· 热点： 异种器官移植；猪作为药代与免疫模型；编辑动物的遗传稳定性与生物安全评估；无病毒载体递送。</t>
+          <t>· 进展： CRISPR/Cas9 + 体细胞核移植（SCNT）在猪上已是成熟流水线；从单基因敲除走向精准敲入、碱基编辑（ABE/CBE）、prime editing。多位点编辑猪（去除免疫原/PERV）已推动猪心、猪肾移植进入人体实质阶段（2022 年以来）。</t>
         </is>
       </c>
     </row>
@@ -704,7 +705,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>· 空白： 大动物脱靶与嵌合体评估无统一标准；疾病模型普遍「建成了但机制没深挖」；成本与世代周期使机制迭代困难；缺少大动物的单细胞/空间图谱。</t>
+          <t>· 热点： 异种器官移植；猪作为药代与免疫模型；编辑动物的遗传稳定性与生物安全评估；无病毒载体递送。</t>
         </is>
       </c>
     </row>
@@ -712,7 +713,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>· 趋势： 模型工程本身正在服务化、商品化——做出一个模型的学术溢价在持续下降，价值转移到「用模型回答机制问题」和「作为转化终点的验证」。</t>
+          <t>· 空白： 大动物脱靶与嵌合体评估无统一标准；疾病模型普遍「建成了但机制没深挖」；成本与世代周期使机制迭代困难；缺少大动物的单细胞/空间图谱。</t>
         </is>
       </c>
     </row>
@@ -720,7 +721,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>· 对你的含义： 这条线技术含量高、工业界可读性强，但作为独立 PI 主线已经偏晚。应定位为工具与终点验证，不作主打。</t>
+          <t>· 趋势： 模型工程本身正在服务化、商品化——做出一个模型的学术溢价在持续下降，价值转移到「用模型回答机制问题」和「作为转化终点的验证」。</t>
         </is>
       </c>
     </row>
@@ -728,27 +729,27 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>· 对你的含义： 这条线技术含量高、工业界可读性强，但作为独立 PI 主线已经偏晚。应定位为工具与终点验证，不作主打。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>English — Pig CRISPR+SCNT is a mature pipeline; the frontier has moved to precise knock-in, base and prime editing, and multiplex-edited donor pigs now in human xenotransplant trials. Open problems: no standardised off-target/mosaicism assessment in large animals, phenotype-only disease models with shallow mechanism, prohibitive cost per iteration, missing single-cell atlases. The trend that matters for you: model building itself is commoditising, so the academic premium has shifted from making a model to answering a mechanistic question with one. Position this as a tool and a translational endpoint, not as your independent line.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>B · 代谢×病毒复制（胆固醇 / 乳酸）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -756,7 +757,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>· 进展： 病毒对宿主脂质与胆固醇通路的依赖（复制细胞器膜、脂筏进入）已确立；SREBP/HMGCR 轴、25-羟胆固醇/CH25H 抗病毒轴清楚；感染细胞的 Warburg 样重编程被广泛报道。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -764,7 +765,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>· 热点： 宿主导向抗病毒药物；乳酸与蛋白乳酰化（lactylation）作为新表观修饰（2019 年后爆发式增长）；代谢-天然免疫交叉（cGAS/STING、RIG-I 的代谢调控）；脂滴生物学。</t>
+          <t>· 进展： 病毒对宿主脂质与胆固醇通路的依赖（复制细胞器膜、脂筏进入）已确立；SREBP/HMGCR 轴、25-羟胆固醇/CH25H 抗病毒轴清楚；感染细胞的 Warburg 样重编程被广泛报道。</t>
         </is>
       </c>
     </row>
@@ -772,7 +773,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>· 空白： 乳酸/乳酰化在 RNA 层面的作用几乎空白；代谢物如何调控 RNA 稳定性与翻译罕有系统研究；兽医病毒（CSFV/PEDV）的机制发现难以进入主流人类疾病语境。</t>
+          <t>· 热点： 宿主导向抗病毒药物；乳酸与蛋白乳酰化（lactylation）作为新表观修饰（2019 年后爆发式增长）；代谢-天然免疫交叉（cGAS/STING、RIG-I 的代谢调控）；脂滴生物学。</t>
         </is>
       </c>
     </row>
@@ -780,7 +781,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>· 趋势： 从「代谢为病毒供料」走向「代谢物作为信号，通过乳酰化/巴豆酰化等修饰直接改写宿主机器」。</t>
+          <t>· 空白： 乳酸/乳酰化在 RNA 层面的作用几乎空白；代谢物如何调控 RNA 稳定性与翻译罕有系统研究；兽医病毒（CSFV/PEDV）的机制发现难以进入主流人类疾病语境。</t>
         </is>
       </c>
     </row>
@@ -788,7 +789,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>· 对你的含义： 你的一作 #8（乳酸→胆固醇→病毒复制）是一条完整的代谢物因果链，方法学可以整体迁移到「代谢物→RNA 降解机器」。但「兽医病毒」这个外壳在北美/欧洲经费体系里是负资产，必须把内核剥出来。</t>
+          <t>· 趋势： 从「代谢为病毒供料」走向「代谢物作为信号，通过乳酰化/巴豆酰化等修饰直接改写宿主机器」。</t>
         </is>
       </c>
     </row>
@@ -796,27 +797,27 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>· 对你的含义： 你的一作 #8（乳酸→胆固醇→病毒复制）是一条完整的代谢物因果链，方法学可以整体迁移到「代谢物→RNA 降解机器」。但「兽医病毒」这个外壳在北美/欧洲经费体系里是负资产，必须把内核剥出来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>English — Viral dependence on host lipid/cholesterol pathways is established (SREBP/HMGCR, CH25H/25-HC), as is Warburg-like rewiring in infected cells. Hot: host-directed antivirals, and lactate/protein lactylation as a post-2019 modification field. The gap that matters: lactate and lactylation have almost no established role at the RNA level, and metabolite control of RNA stability is barely studied. Your first-author lactate→cholesterol→replication chain is a complete metabolite-to-phenotype causal argument and transfers wholesale; but the "veterinary virus" packaging is a liability in US/EU funding — extract the core and drop the shell.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>C · 器官纤维化</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -824,7 +825,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>· 进展： 共同通路清楚（TGF-β/SMAD、YAP/TAZ 机械转导、成纤维细胞→肌成纤维细胞转化）；单细胞图谱已定义病理性成纤维细胞亚群；但获批抗纤维化药只有 nintedanib 与 pirfenidone，且仅限肺（IPF）——心、肠、肝纤维化零获批药。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -832,7 +833,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>· 热点： 纤维化的可逆性与消退（resolution）；成纤维细胞的代谢重编程（糖酵解/乳酸依赖）；机械力-代谢耦合；器官特异机制 vs 共同机制；类器官与 fibrosis-on-chip 药筛。</t>
+          <t>· 进展： 共同通路清楚（TGF-β/SMAD、YAP/TAZ 机械转导、成纤维细胞→肌成纤维细胞转化）；单细胞图谱已定义病理性成纤维细胞亚群；但获批抗纤维化药只有 nintedanib 与 pirfenidone，且仅限肺（IPF）——心、肠、肝纤维化零获批药。</t>
         </is>
       </c>
     </row>
@@ -840,7 +841,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>· 空白： 肠纤维化（IBD 狭窄）机制与药物极度缺乏；抗纤维化 miR-29 已知十余年却未成药——「递送」和「为什么内源 miR-29 在纤维化时被关掉」两个问题都没解；极少有实验室能在同一套逻辑下横向比较心脏与肠道纤维化。</t>
+          <t>· 热点： 纤维化的可逆性与消退（resolution）；成纤维细胞的代谢重编程（糖酵解/乳酸依赖）；机械力-代谢耦合；器官特异机制 vs 共同机制；类器官与 fibrosis-on-chip 药筛。</t>
         </is>
       </c>
     </row>
@@ -848,7 +849,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>· 趋势： 从抑制活化转向促进消退；靶向成纤维细胞代谢；RNA 疗法（miRNA mimic / antagomiR / ASO）。</t>
+          <t>· 空白： 肠纤维化（IBD 狭窄）机制与药物极度缺乏；抗纤维化 miR-29 已知十余年却未成药——「递送」和「为什么内源 miR-29 在纤维化时被关掉」两个问题都没解；极少有实验室能在同一套逻辑下横向比较心脏与肠道纤维化。</t>
         </is>
       </c>
     </row>
@@ -856,7 +857,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>· 对你的含义： 这是你现有资产里领域需求最强、你位置最扎实的一条——两个不同器官的一作论文 + 自己当 PI 的基金。而「内源 miR-29 为什么被关掉」这个公认空白，恰好是你能用 RNA 降解机制去回答的。</t>
+          <t>· 趋势： 从抑制活化转向促进消退；靶向成纤维细胞代谢；RNA 疗法（miRNA mimic / antagomiR / ASO）。</t>
         </is>
       </c>
     </row>
@@ -864,27 +865,27 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>· 对你的含义： 这是你现有资产里领域需求最强、你位置最扎实的一条——两个不同器官的一作论文 + 自己当 PI 的基金。而「内源 miR-29 为什么被关掉」这个公认空白，恰好是你能用 RNA 降解机制去回答的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>English — Core pathways (TGF-β/SMAD, YAP/TAZ, myofibroblast conversion) and pathological fibroblast subsets are well mapped, yet only two drugs are approved, both lung-only; cardiac, intestinal and hepatic fibrosis have none. Hot: fibrosis resolution, fibroblast metabolic rewiring, mechano-metabolic coupling, organoid/organ-chip screening. Key gaps: intestinal fibrosis (IBD strictures) is mechanistically and therapeutically bare; anti-fibrotic miR-29 has been known for over a decade without becoming a drug — neither delivery nor "why is endogenous miR-29 switched off in fibrosis" is solved; and almost no lab compares heart and gut fibrosis under one framework. This is the strongest-demand, best-owned position among your existing assets — and that open question is exactly one an RNA-decay mechanism can answer.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>D · 胃癌代谢/钙稳态与 lncRNA-Wnt 轴</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -892,7 +893,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>· 进展： 胃癌分子分型（TCGA：EBV / MSI / GS / CIN）成熟；PD-1 抑制剂联合化疗已成一线；Claudin18.2 靶向（CAR-T、ADC）是当前最热转化方向。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -900,7 +901,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>· 热点： MSI/dMMR 与免疫治疗响应；Claudin18.2；肿瘤-免疫代谢耦合；胃癌类器官药敏。</t>
+          <t>· 进展： 胃癌分子分型（TCGA：EBV / MSI / GS / CIN）成熟；PD-1 抑制剂联合化疗已成一线；Claudin18.2 靶向（CAR-T、ADC）是当前最热转化方向。</t>
         </is>
       </c>
     </row>
@@ -908,7 +909,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>· 空白： 钙稳态与代谢偏移在胃癌中的因果关系研究薄弱；dystrophin（DMD）作为胃癌相关基因几乎无人研究——这是你自己的发现，冷门而新。</t>
+          <t>· 热点： MSI/dMMR 与免疫治疗响应；Claudin18.2；肿瘤-免疫代谢耦合；胃癌类器官药敏。</t>
         </is>
       </c>
     </row>
@@ -916,7 +917,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>· 直言不讳： 你参与的三项基金（VAX2/SNHG9/WNT2B、Linc01189、Linc02139）走的是 「lncRNA → Wnt/糖酵解」 这条路。这条赛道极度拥挤、可重复性长期受质疑、转化产出极低，而且你在基金里是第 2–3 负责人而非负责人。它不构成 PI 叙事，建议不列入未来方向。</t>
+          <t>· 空白： 钙稳态与代谢偏移在胃癌中的因果关系研究薄弱；dystrophin（DMD）作为胃癌相关基因几乎无人研究——这是你自己的发现，冷门而新。</t>
         </is>
       </c>
     </row>
@@ -924,7 +925,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>· 对你的含义： 保留 #4 那篇一作作为「我能做肿瘤代谢」的证据即可；lncRNA 那一摊主动退出。</t>
+          <t>· 直言不讳： 你参与的三项基金（VAX2/SNHG9/WNT2B、Linc01189、Linc02139）走的是 「lncRNA → Wnt/糖酵解」 这条路。这条赛道极度拥挤、可重复性长期受质疑、转化产出极低，而且你在基金里是第 2–3 负责人而非负责人。它不构成 PI 叙事，建议不列入未来方向。</t>
         </is>
       </c>
     </row>
@@ -932,27 +933,27 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t>· 对你的含义： 保留 #4 那篇一作作为「我能做肿瘤代谢」的证据即可；lncRNA 那一摊主动退出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>English — Molecular subtyping is settled, PD-1+chemo is first line, Claudin18.2 is the hot translational axis. Genuine gap: calcium-homeostasis/metabolic-shift causality is thin, and dystrophin as a gastric-cancer gene is essentially unstudied — your own, genuinely novel, and unfashionable finding. Blunt assessment: the three funded projects you are on run the lncRNA→Wnt/glycolysis route — an extremely crowded track with chronic reproducibility criticism and very low translational yield, on which you are 2nd/3rd investigator, not the lead. It will not carry a PI narrative. Keep paper #4 as evidence of tumour-metabolism competence and exit the lncRNA work deliberately.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E · 类器官与碱基编辑平台</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -960,7 +961,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>· 进展： 类器官已从肠道扩展到几乎全器官；类器官生物库的药敏结果已有前瞻性临床相关数据；碱基编辑已进入临床（心血管、血液病方向）。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -968,7 +969,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>· 热点： 类器官+免疫/微生物共培养；器官芯片；高通量类器官筛选；prime editing 与表观编辑；体内递送（LNP/AAV）。</t>
+          <t>· 进展： 类器官已从肠道扩展到几乎全器官；类器官生物库的药敏结果已有前瞻性临床相关数据；碱基编辑已进入临床（心血管、血液病方向）。</t>
         </is>
       </c>
     </row>
@@ -976,7 +977,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>· 空白： 类器官批次异质性与定量标准；把「编辑+类器官」用于 RNA 调控层（而非编码基因）的研究很少见。</t>
+          <t>· 热点： 类器官+免疫/微生物共培养；器官芯片；高通量类器官筛选；prime editing 与表观编辑；体内递送（LNP/AAV）。</t>
         </is>
       </c>
     </row>
@@ -984,7 +985,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>· 趋势： 平台本身快速商品化 → 差异化价值落在独特读出系统（报告系统）与独特疾病模型上。</t>
+          <t>· 空白： 类器官批次异质性与定量标准；把「编辑+类器官」用于 RNA 调控层（而非编码基因）的研究很少见。</t>
         </is>
       </c>
     </row>
@@ -992,7 +993,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>· 直言不讳： 你这条线的 3 篇是书章节、末位作者。对基金评审它们是「方法可行性」的好证据，但绝不能当成 3 篇通讯作者研究论文来展示——评审会查期刊类型，一查就露。</t>
+          <t>· 趋势： 平台本身快速商品化 → 差异化价值落在独特读出系统（报告系统）与独特疾病模型上。</t>
         </is>
       </c>
     </row>
@@ -1000,27 +1001,27 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
+          <t>· 直言不讳： 你这条线的 3 篇是书章节、末位作者。对基金评审它们是「方法可行性」的好证据，但绝不能当成 3 篇通讯作者研究论文来展示——评审会查期刊类型，一查就露。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>English — Organoids now span nearly all organs, biobank drug-response data has prospective clinical correlation, and base editing has reached the clinic. Hot: immune/microbial co-culture, organ-on-chip, high-throughput screening, prime and epigenome editing, in-vivo delivery. Gaps: batch heterogeneity and quantitative standards; and very little work applies editing+organoids to the RNA-regulatory layer rather than to coding genes. As platforms commoditise, differentiation moves to unique read-outs (reporters) and unique disease models. Blunt: your three items here are last-author book chapters. Excellent feasibility evidence — but presenting them as corresponding-author research papers will not survive a reviewer checking the journal type.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>F · 小 RNA 生物学与 miRNA 降解</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>中文</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1029,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>· 进展： miRNA 生成通路（DROSHA/DGCR8/DICER/AGO）已是教科书内容。近五年领域重心明确转向miRNA 的降解与末端修饰：靶标导向的 miRNA 降解（TDMD）由 ZSWIM8–Cul3 泛素连接酶介导（2020 年确立）；TUT4/7 的尿苷化、AGO2 的稳定性构成另一层控制；2026 年 ZSWIM8–AGO2–靶标复合体的冷冻电镜结构问世，机制细节进入结构时代。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1037,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>· 热点： TDMD 的生理功能与体内相关性；miRNA 半衰期的组织特异调控；非经典 miRNA 生成；miRNA 治疗（递送仍是瓶颈）。</t>
+          <t>· 进展： miRNA 生成通路（DROSHA/DGCR8/DICER/AGO）已是教科书内容。近五年领域重心明确转向miRNA 的降解与末端修饰：靶标导向的 miRNA 降解（TDMD）由 ZSWIM8–Cul3 泛素连接酶介导（2020 年确立）；TUT4/7 的尿苷化、AGO2 的稳定性构成另一层控制；2026 年 ZSWIM8–AGO2–靶标复合体的冷冻电镜结构问世，机制细节进入结构时代。</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1045,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>· 空白（这是最关键的一句）： 上游信号——激酶、代谢状态、翻译后修饰——如何调控 miRNA 降解机器，几乎是空白。 绝大多数 TDMD 研究在细胞系里做「机器怎么工作」，很少有人问「机器什么时候被打开」。此外 TDMD 在疾病中的因果作用极少在类器官/大动物层面验证；ZSWIM8 的底物识别「语法」未解。</t>
+          <t>· 热点： TDMD 的生理功能与体内相关性；miRNA 半衰期的组织特异调控；非经典 miRNA 生成；miRNA 治疗（递送仍是瓶颈）。</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1053,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>· 趋势： 从机制发现走向生理与疾病情境；从细胞系走向组织与体内；信号通路对小 RNA 稳态的控制。</t>
+          <t>· 空白（这是最关键的一句）： 上游信号——激酶、代谢状态、翻译后修饰——如何调控 miRNA 降解机器，几乎是空白。 绝大多数 TDMD 研究在细胞系里做「机器怎么工作」，很少有人问「机器什么时候被打开」。此外 TDMD 在疾病中的因果作用极少在类器官/大动物层面验证；ZSWIM8 的底物识别「语法」未解。</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1061,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>· 对你的位置的判断： 边缘。 一篇第 2 作者、零一作。但那个空白（上游信号 → miRNA 降解）恰好是你 A–E 五条线的交集——这是本报告最重要的结构性发现。</t>
+          <t>· 趋势： 从机制发现走向生理与疾病情境；从细胞系走向组织与体内；信号通路对小 RNA 稳态的控制。</t>
         </is>
       </c>
     </row>
@@ -1068,19 +1069,15 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
+          <t>· 对你的位置的判断： 边缘。 一篇第 2 作者、零一作。但那个空白（上游信号 → miRNA 降解）恰好是你 A–E 五条线的交集——这是本报告最重要的结构性发现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>English — Biogenesis is textbook; the field's centre of gravity has moved to miRNA decay and 3′-end modification: target-directed miRNA degradation (TDMD) via the ZSWIM8–Cul3 ubiquitin ligase (established 2020), TUT4/7 uridylation, AGO2 stability; a 2026 cryo-EM structure of the ZSWIM8–AGO2–target complex has pushed mechanism into the structural era. Hot: physiological relevance of TDMD, tissue-specific miRNA half-life control, non-canonical biogenesis, miRNA therapeutics. The decisive gap: how upstream signalling — kinases, metabolic state, post-translational modification — controls the decay machinery is almost unstudied. Most TDMD work asks how the machine works in cell lines; very few ask when it is switched on. Your position here is marginal (one second-author paper, no first-author). But that gap is precisely the intersection of your other five lines — the most important structural finding in this report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>3 · 我的研究定位 / My Research Positioning</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1089,19 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>3 · 我的研究定位 / My Research Positioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>中文 + English（双语表，只列一份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>一句话定位： 你不是「方向分散」，你是资产集中在 B+C，身份却押在 F——两者之间缺一篇论文把它们焊起来。</t>
         </is>
       </c>
     </row>
@@ -1108,19 +1109,15 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" s="3" t="inlineStr">
         <is>
+          <t>一句话定位： 你不是「方向分散」，你是资产集中在 B+C，身份却押在 F——两者之间缺一篇论文把它们焊起来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>One-line positioning: Your problem is not scattered interests; it is that your assets sit in B+C while your identity is staked on F, with no paper yet welding the two together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>4 · 可持续发展评估 / Sustainability Assessment</t>
         </is>
       </c>
     </row>
@@ -1132,15 +1129,19 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t>4 · 可持续发展评估 / Sustainability Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>评分维度各 1–5 分：①未来 5–10 年空间 ②能否支撑实验室持续产出（子问题与学生课题数量） ③竞争格局与可建壁垒 ④经费/数据/合作资源可持续性。综合分为四项均值。评分是我的主观量化，不是客观指标。</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1149,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>三条硬话：</t>
+          <t>评分维度各 1–5 分：①未来 5–10 年空间 ②能否支撑实验室持续产出（子问题与学生课题数量） ③竞争格局与可建壁垒 ④经费/数据/合作资源可持续性。综合分为四项均值。评分是我的主观量化，不是客观指标。</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1157,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>· 你现在同时挂着 6 条线，其中 2 条（D 的 lncRNA、A 的模型工程）在消耗你的时间但不增加你的议价能力。 早期 PI 最贵的资源是注意力，不是钱。</t>
+          <t>三条硬话：</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1165,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>· F 是你唯一分数满格的空间方向，也是你唯一零一作的方向。 这个矛盾不解决，其他规划都是空的。</t>
+          <t>· 你现在同时挂着 6 条线，其中 2 条（D 的 lncRNA、A 的模型工程）在消耗你的时间但不增加你的议价能力。 早期 PI 最贵的资源是注意力，不是钱。</t>
         </is>
       </c>
     </row>
@@ -1172,27 +1173,27 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
+          <t>· F 是你唯一分数满格的空间方向，也是你唯一零一作的方向。 这个矛盾不解决，其他规划都是空的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
           <t>· C 是你唯一「今天就能去谈 offer」的方向。 它应该负责养活实验室，让 F 去冒险。</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>English</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Scores (1–5, my subjective quantification, not an objective index) on: headroom over 5–10 years; capacity to sustain lab throughput; competitive moat; and durability of funding/data/collaboration. See the bilingual table above.</t>
         </is>
       </c>
     </row>
@@ -1200,39 +1201,35 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" s="3" t="inlineStr">
         <is>
+          <t>Scores (1–5, my subjective quantification, not an objective index) on: headroom over 5–10 years; capacity to sustain lab throughput; competitive moat; and durability of funding/data/collaboration. See the bilingual table above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>Three blunt points: (1) you are carrying six lines, two of which (D's lncRNA work, A's model engineering) consume time without increasing your bargaining power — attention, not money, is an early PI's scarcest resource; (2) F is simultaneously your only maximum-headroom direction and your only direction with zero first-author output — until that contradiction is resolved, every other plan is hypothetical; (3) C is the only direction on which you could negotiate an offer today — it should fund the lab so that F can take risk.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>5 · 未来研究方向建议（核心）/ Recommended Future Directions</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>三个方向共用一个统一叙事：「代谢与信号状态如何通过控制 miRNA 的降解与末端修饰，决定慢性疾病的可逆性」，并共用 miR-29 作为核心 miRNA，使三者在同一份申请书里互为 Aim 而不互相稀释。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>方向 1（最高优先）· 能量应激对 miRNA 降解机器的控制：AMPK–ZSWIM8–代谢记忆</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1241,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>方向 2 · 抗纤维化 miRNA 的末端修饰检查点：TUT4/7–miR-29（最快出成果）</t>
+          <t>方向 1（最高优先）· 能量应激对 miRNA 降解机器的控制：AMPK–ZSWIM8–代谢记忆</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1253,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>方向 3 · 乳酸/乳酰化对小 RNA 稳态的调控（你的身份标签方向）</t>
+          <t>方向 2 · 抗纤维化 miRNA 的末端修饰检查点：TUT4/7–miR-29（最快出成果）</t>
         </is>
       </c>
     </row>
@@ -1268,27 +1265,27 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
+          <t>方向 3 · 乳酸/乳酰化对小 RNA 稳态的调控（你的身份标签方向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>同时必须做的「减法」/ What to drop</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>English summary of §5 — Three directions under one narrative ("how metabolic and signalling state, acting through miRNA decay and 3′-end modification, sets the reversibility of chronic disease"), sharing miR-29 as the keystone so they function as Aims of one application rather than diluting each other. Direction 1 (top priority): AMPK phosphorylation of ZSWIM8 driving TDMD of metabolic miRNAs as a mechanism for metabolic memory — a fusion of B, F and A/E, with a 4-D sub-problem grid, a 12-month go/no-go on kinase assay plus half-life measurement, and an explicit fallback. Direction 2 (fastest output): TUT4/7 uridylation of miR-29 as a druggable fibrosis checkpoint, startable on banked samples from your own two published organ models, first paper plausible in 9–12 months. Direction 3 (identity marker): lactate/lactylation control of AGO2/ZSWIM8/TUT4-7 — nearly unoccupied, uses your unique lactate tooling, but needs a mass-spectrometry collaborator, so run it as Aim 3 rather than standalone. Simultaneously drop the lncRNA gastric-cancer line, demote veterinary virology to background evidence, demote large-animal and organoid platforms to feasibility tooling, and stop describing the three protocol chapters as corresponding-author papers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>6 · 文献阅读规划 / Literature Reading Plan</t>
         </is>
       </c>
     </row>
@@ -1300,27 +1297,27 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
+          <t>6 · 文献阅读规划 / Literature Reading Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>经本项目核实过的锚点文献（PMID 已验证）/ Verified anchor references</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>这些 PMID 是本项目此前通过 Europe PMC 逐条核实的，可以直接去查，不是我凭记忆写的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>阅读顺序与时间安排 / Reading order and time budget</t>
         </is>
       </c>
     </row>
@@ -1328,15 +1325,19 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>2026-09-29 更新 —— 这一节的粗排已被 §13 的逐周计划取代，且 68 篇笔记已全部按全文填好。 68 篇 × 14 栏已无任何一栏标着「需读全文核对」：43 篇来自 Europe PMC / NCBI PMC 开放全文， 22 篇来自我自己下载的 PDF（含 MMB 2141 第 40 章 Phos-tag SDS-PAGE、MMB 3059 第 9 章肠类器官方案）， 3 篇因原文无开放全文换成了同角色替代文献（层级一并降为 T2，不当等价替换）。 核对方式：开放全文那 43 篇里 ⑭栏引用的 127 个 PMID 全部出自该文自己的参考文献表； PDF 篇与替代篇的引用标题全部能在该文全文逐字回查到；③栏图号全部能对应。 所以下面这张 6 段式粗排只作为背景保留，实际执行按 §13.1 的十二周表。</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>必读的经典工作类型（不列具体标题以免编造）： ①miRNA 降解机器的遗传学筛选类论文；②miRNA 半衰期的系统测定类论文；③AMPK 底物识别基序的生化确立类论文；④纤维化中成纤维细胞命运决定的单细胞图谱类论文；⑤类器官纤维化模型的方法学论文。</t>
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>阅读顺序与时间安排（粗排，已被 §13 取代）/ Reading order and time budget</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1345,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>需要补的交叉学科知识： ①激酶生化与底物特异性的基本判据（什么算「直接磷酸化」的证据链）；②RNA 稳定性测定的统计与建模（半衰期拟合、归一化陷阱）；③蛋白组学与修饰位点鉴定的基本读法（FDR、位点定位概率）；④纤维化的临床终点与药物评价标准（为写转化意义）。</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -1352,47 +1353,47 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
+          <t>必读的经典工作类型（不列具体标题以免编造）： ①miRNA 降解机器的遗传学筛选类论文；②miRNA 半衰期的系统测定类论文；③AMPK 底物识别基序的生化确立类论文；④纤维化中成纤维细胞命运决定的单细胞图谱类论文；⑤类器官纤维化模型的方法学论文。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>需要补的交叉学科知识： ①激酶生化与底物特异性的基本判据（什么算「直接磷酸化」的证据链）；②RNA 稳定性测定的统计与建模（半衰期拟合、归一化陷阱）；③蛋白组学与修饰位点鉴定的基本读法（FDR、位点定位概率）；④纤维化的临床终点与药物评价标准（为写转化意义）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
           <t>English — Start with the TDMD review (38224449), then the two 2020 *Science* papers and the *Cell* 2018 physiological case (weeks 1–2); map the machine's boundaries including the 2026 cryo-EM structure, checking whether the disordered region carrying S608/S609 is accessible (weeks 3–4); then spend weeks 5–6 on your actual gap — AMPK substrate recognition and upstream signalling — and produce a one-page memo stating explicitly why nobody has connected signalling to miRNA decay; weeks 7–8 on metabolic memory for the Significance narrative; weeks 9–10 on uridylation and miR-29 fibrosis for Direction 2; weeks 11–12 on lactylation to decide whether Direction 3 is feasible at all. Maintain standing PubMed/bioRxiv alerts on the six keyword strings listed above, 30 minutes every Friday, one field-movement note per month. Classic-work *categories* to read (titles deliberately not invented): genetic screens for decay machinery; systematic miRNA half-life measurement; biochemical establishment of AMPK substrate motifs; single-cell fibroblast-fate atlases in fibrosis; organoid fibrosis methodology. Cross-disciplinary knowledge to acquire: kinase biochemistry and what counts as a direct-phosphorylation evidence chain; statistics of RNA-stability measurement (half-life fitting, normalisation traps); how to read proteomics site-localisation output; and clinical endpoints in fibrosis for the translational argument.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>7 · 实验技术学习规划 / Experimental &amp; Technical Learning Plan</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>中文 + English（双语表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>两个别人想不到、但你独有的技能迁移：</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>· 杂交瘤单克隆抗体制备（CV 明确列出）→ 你可以自己做 phospho-ZSWIM8(S608) 特异抗体。 这个方向最大的技术瓶颈就是「没有好的磷酸化抗体」，而这恰好是你的现成技能。这可能是本报告里性价比最高的一条建议。</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1401,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>· 碱基编辑（ABE/BE4） → 在内源位点做 Ser→Ala / Ser→Asp 敲入，而不是用过表达质粒。审稿人对「内源位点点突变」的信任度远高于过表达，而多数 RNA 实验室做不到这一点。</t>
+          <t>两个别人想不到、但你独有的技能迁移：</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1409,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>需要合作者补位的四处： ①质谱蛋白组学（必需）；②结构生物学（若要谈位点可及性）；③人纤维化临床样本（增强转化说服力）；④统计/生信深度（若要做全局半衰期建模）。</t>
+          <t>· 杂交瘤单克隆抗体制备（CV 明确列出）→ 你可以自己做 phospho-ZSWIM8(S608) 特异抗体。 这个方向最大的技术瓶颈就是「没有好的磷酸化抗体」，而这恰好是你的现成技能。这可能是本报告里性价比最高的一条建议。</t>
         </is>
       </c>
     </row>
@@ -1416,79 +1417,75 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
+          <t>· 碱基编辑（ABE/BE4） → 在内源位点做 Ser→Ala / Ser→Asp 敲入，而不是用过表达质粒。审稿人对「内源位点点突变」的信任度远高于过表达，而多数 RNA 实验室做不到这一点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>需要合作者补位的四处： ①质谱蛋白组学（必需）；②结构生物学（若要谈位点可及性）；③人纤维化临床样本（增强转化说服力）；④统计/生信深度（若要做全局半衰期建模）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
           <t>English — The critical gap is small-RNA methodology, and it is learnable inside your current lab at zero cost: small-RNA library prep and independent analysis (2–3 months), Act-D half-life measurement validated first on a known short-lived miRNA (1 month), AGO-RIP (1–2 months, skip iCLIP). Kinase biochemistry needs 2–3 months and should be learned once alongside a biochemistry/structural group — and any in-vitro kinase experiment must run a canonical AMPK substrate on the same gel, or a negative result carries no information. Phospho/lactyl mass spectrometry should not be done hands-on: secure the institutional core and learn to judge site-localisation confidence. Two skill transfers nobody would anticipate: your hybridoma monoclonal-antibody capability means you can raise your own phospho-ZSWIM8(S608) antibody — the field's main technical bottleneck is the absence of good phospho-antibodies, which makes this probably the highest-leverage single recommendation in this report; and your base-editing stack lets you install Ser→Ala/Ser→Asp at the endogenous locus rather than relying on overexpression, which reviewers trust far more and most RNA labs cannot do. Collaborators are genuinely required for proteomics (mandatory), structural biology (if arguing site accessibility), human fibrosis specimens, and deep computational modelling.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>8 · 未来 12 个月行动清单 / 12-Month Action Plan</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>中文 + English（双语表）</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>关于顺序的一句话： Q1 的第 ② 项（向 Lai 谈清楚问题归属）是整张表的唯一单点故障。如果那次谈话结果是「这个问题属于实验室」，Q2–Q4 全部需要重排——所以它必须在第 1 个月内发生，而不是拖到第 3 个月。</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>English — Q1: close the reading gap and produce the one-page memo; put a one-page side-project proposal to your PI for a question you own, explicitly negotiating whether you can take it with you; learn small-RNA library prep in-lab and analyse one dataset end-to-end; start Direction 2 at zero cost by measuring miR-29 in your own banked heart and gut samples. Q2: the go/no-go — metabolic perturbation plus Act-D chase plus small-RNA seq for half-life change, and an in-vitro kinase assay on recombinant ZSWIM8 fragments (WT vs S→A) with a canonical substrate as same-gel positive control; submit miR-29 3′-end sequencing; start the phospho-S608 hybridoma now because the timeline is long; and submit one of the Asian fellowships against its real deadline using the six complete drafts already produced in this project. Q3: expand to 2–3 systems (or pivot to Direction 2 if Q2 was negative), install S608A/S608D at the endogenous locus by base editing, write the one thesis-defining review fusing metabolic signalling, small-RNA homeostasis and fibrosis, recruit two co-corresponding collaborators, and submit a conference abstract — your conference record is currently one talk and one poster, a visibility weakness. Q4: submit the first-author paper, draft the second, write the 2-page Specific Aims and run the "do you own this question?" test past three PIs, lock three corresponding-author-level referees across your three institutions, and launch applications. Sequencing note: the ownership conversation in Q1 is the single point of failure for the whole table — if the answer is "the question belongs to the lab", Q2–Q4 must be replanned, so it has to happen in month 1, not month 3.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>9 · 一句话结论 / One-Sentence Conclusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>现在最该做的一件事：在 Lai lab 用「代谢/能量信号如何改变 miRNA 半衰期」这个属于你自己的问题，拿到一篇你的一作论文——因为你其余所有资产（两器官纤维化、代谢因果链、大动物、编辑、类器官、以及已经当过 PI 的基金记录）已经足够支撑一个实验室了，唯一缺的，是把「我在 RNA 前沿有一个自己的问题」变成一件可以被引用的事实。</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1497,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>中文</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1505,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>The single most important thing to do now: get one first-author paper out of Lai lab on a question that is yours — how metabolic/energy signalling changes miRNA half-life — because every other asset you have (two-organ fibrosis record, metabolite causality, large-animal models, editing, organoids, and a grant you already held as PI) is already enough to support a lab; the only thing missing is turning "I own a question at the RNA frontier" into a citable fact.</t>
+          <t>现在最该做的一件事：在 Lai lab 用「代谢/能量信号如何改变 miRNA 半衰期」这个属于你自己的问题，拿到一篇你的一作论文——因为你其余所有资产（两器官纤维化、代谢因果链、大动物、编辑、类器官、以及已经当过 PI 的基金记录）已经足够支撑一个实验室了，唯一缺的，是把「我在 RNA 前沿有一个自己的问题」变成一件可以被引用的事实。</t>
         </is>
       </c>
     </row>
@@ -1520,35 +1517,39 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>The single most important thing to do now: get one first-author paper out of Lai lab on a question that is yours — how metabolic/energy signalling changes miRNA half-life — because every other asset you have (two-organ fibrosis record, metabolite causality, large-animal models, editing, organoids, and a grant you already held as PI) is already enough to support a lab; the only thing missing is turning "I own a question at the RNA frontier" into a citable fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>10 · 资料充分性与缺口 / Data Sufficiency and Gaps</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>样本是否充分：充分。 解析出 17 篇发表（&gt;5 篇门槛）、9 项基金、完整技能清单与履历时间线。第 1–5 节的结论有真实资料支撑。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>必须更正的一处（已在报告开头声明）： 本项目此前 positioning_brief.md 的「~11 first-author」为错误计数。按 CV 逐条核对：一作 7、末位 3（全为书章节）、中间 7。</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1557,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>数字上的一处不一致，请你确认： 两处记录的引用数不同 —— 一处记 669 引 / h=10，一处记 675 引。这是抓取日期不同造成的，用于申请书前请你自己去 Scholar 看当日值。此外 PhD 期有三篇方法学论文处于 60–130 引区间，但我没有逐篇核对哪个数对应哪篇，所以本报告不给它们分配引用数。</t>
+          <t>样本是否充分：充分。 解析出 17 篇发表（&gt;5 篇门槛）、9 项基金、完整技能清单与履历时间线。第 1–5 节的结论有真实资料支撑。</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1565,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>明确属于推测、不是从你资料推出的结论：</t>
+          <t>必须更正的一处（已在报告开头声明）： 本项目此前 positioning_brief.md 的「~11 first-author」为错误计数。按 CV 逐条核对：一作 7、末位 3（全为书章节）、中间 7。</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1573,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>· 第 2 节所有「领域进展/热点/空白/趋势」出自我的领域知识；</t>
+          <t>数字上的一处不一致，请你确认： 两处记录的引用数不同 —— 一处记 669 引 / h=10，一处记 675 引。这是抓取日期不同造成的，用于申请书前请你自己去 Scholar 看当日值。此外 PhD 期有三篇方法学论文处于 60–130 引区间，但我没有逐篇核对哪个数对应哪篇，所以本报告不给它们分配引用数。</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1581,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>· 第 4 节的可持续性评分是我的主观量化，不是客观指标；</t>
+          <t>2026-09-29 已关闭的一处缺口： 阅读计划里那 68 篇的「关键图与可信度／做了漏了哪些对照／效应量／要排队的参考文献」四栏此前标着「需读全文核对」——现已全部按全文填写（43 篇开放全文 + 22 篇你下载的 PDF + 3 篇替代文献），并做了两道机械核对（引用的 127 个 PMID 全部出自各文自己的参考文献表；PDF 篇与替代篇的引用标题可在全文逐字回查）。另把 4 处「对作者/单位的猜测」按全文作者名单改写成实证或「全文未给出」。</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1589,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>· 方向 1 的机制假设与 S608/S609 位点预测是假设生成级（来自本项目自建的透明 PSSM，分值本身不构成证据）；</t>
+          <t>读全文后新暴露的三处缺口（此前看摘要看不出来）：</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1597,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>· 各方向的产出时间（9–12 个月、12–18 个月等）是基于常规实验周期的估计。</t>
+          <t>明确属于推测、不是从你资料推出的结论：</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1605,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>需要你补充的材料（按重要性排序）：</t>
+          <t>· 第 2 节所有「领域进展/热点/空白/趋势」出自我的领域知识；</t>
         </is>
       </c>
     </row>
@@ -1612,19 +1613,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>一处 CV 层面的直接建议： CV 最后的 ADDITIONAL / Certifications 一行（高级营养师、心理咨询师、幼儿园园长证、小儿推拿师）建议从学术版 CV 中删除。在 faculty / fellowship 评审语境下它不增加可信度，反而会引出「注意力是否分散」的疑问。这些证书在其他场合有价值，但不在这份 CV 里。</t>
+          <t>· 第 4 节的可持续性评分是我的主观量化，不是客观指标；</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>· 方向 1 的机制假设与 S608/S609 位点预测是假设生成级（来自本项目自建的透明 PSSM，分值本身不构成证据）；</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1629,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Sufficiency: adequate. 17 publications (well above the 5-paper threshold), 9 funded projects, a full skills inventory and a complete career timeline were parsed; sections 1–5 rest on real material.</t>
+          <t>· 各方向的产出时间（9–12 个月、12–18 个月等）是基于常规实验周期的估计。</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1637,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>One correction, stated at the top: the earlier positioning_brief.md count of "~11 first-author" is wrong. Per-paper author-position counting on the CV gives 7 first-author, 3 last-author (all book chapters), 7 middle-author.</t>
+          <t>需要你补充的材料（按重要性排序）：</t>
         </is>
       </c>
     </row>
@@ -1648,15 +1645,19 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>One numeric inconsistency for you to resolve: two records give 669 citations/h=10 and 675 citations respectively — a scrape-date artefact. Check the live value on Scholar before putting any number in an application. Three PhD-era methods papers sit in the 60–130 citation range, but I did not verify which count belongs to which paper, so this report assigns none.</t>
+          <t>一处 CV 层面的直接建议： CV 最后的 ADDITIONAL / Certifications 一行（高级营养师、心理咨询师、幼儿园园长证、小儿推拿师）建议从学术版 CV 中删除。在 faculty / fellowship 评审语境下它不增加可信度，反而会引出「注意力是否分散」的疑问。这些证书在其他场合有价值，但不在这份 CV 里。</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Explicitly speculative, not derived from your materials: (1) every "progress/hot/gap/trend" judgement in §2 comes from my field knowledge; (2) the sustainability scores in §4 are my subjective quantification, not an objective index; (3) the Direction 1 mechanism and the S608/S609 site predictions are hypothesis-generating only — they come from a transparent PSSM built in this project, and the score itself is not evidence; (4) all timelines (9–12 months, 12–18 months) are estimates from conventional experimental cycles.</t>
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1665,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>What you need to supply, in priority order: (1) the ownership boundary your PI will agree to for a side project — the single point of failure in §8, and the determinant of whether the independence narrative holds; (2) your visa/immigration status, which decides whether the US route retains any meaning (K99 effectively closed, F32 requires citizenship/permanent residency) and sets the clock on the Asian route; (3) a real inventory of unpublished data — you previously stated there is none on the ZSWIM8 line, but data elsewhere would reshape the Q1–Q2 schedule; (4) whether the banked MYBPC3 heart and SAA3 gut tissues still exist and who controls them, on which the "zero-cost start" of Direction 2 entirely depends; (5) a teaching/mentoring record, required for faculty applications and currently absent; (6) exact age and months-since-PhD, since the Asian schemes have hard ceilings; (7) a referee list with their willingness confirmed.</t>
+          <t>Sufficiency: adequate. 17 publications (well above the 5-paper threshold), 9 funded projects, a full skills inventory and a complete career timeline were parsed; sections 1–5 rest on real material.</t>
         </is>
       </c>
     </row>
@@ -1672,19 +1673,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>One direct CV recommendation: delete the final ADDITIONAL / Certifications line (advanced nutritionist, psychological counsellor, kindergarten principal, paediatric massage). In a faculty or fellowship review it adds no credibility and invites a question about divided attention. Those certificates have value elsewhere — not on this document.</t>
+          <t>One correction, stated at the top: the earlier positioning_brief.md count of "~11 first-author" is wrong. Per-paper author-position counting on the CV gives 7 first-author, 3 last-author (all book chapters), 7 middle-author.</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>11 · 双语输出说明 / Note on Bilingual Output</t>
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>One numeric inconsistency for you to resolve: two records give 669 citations/h=10 and 675 citations respectively — a scrape-date artefact. Check the live value on Scholar before putting any number in an application. Three PhD-era methods papers sit in the 60–130 citation range, but I did not verify which count belongs to which paper, so this report assigns none.</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1689,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>本报告各节均为中文在前、英文在后。表格采用中英双语表头与双语单元格，只列一份，而非同一张表重复中英两遍——这是对「双语输出」要求的一处有意压缩，目的是让表格可读；如需完全分离的中英两份文件，说一声即可生成。</t>
+          <t>Explicitly speculative, not derived from your materials: (1) every "progress/hot/gap/trend" judgement in §2 comes from my field knowledge; (2) the sustainability scores in §4 are my subjective quantification, not an objective index; (3) the Direction 1 mechanism and the S608/S609 site predictions are hypothesis-generating only — they come from a transparent PSSM built in this project, and the score itself is not evidence; (4) all timelines (9–12 months, 12–18 months) are estimates from conventional experimental cycles.</t>
         </is>
       </c>
     </row>
@@ -1700,59 +1697,55 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
+          <t>What you need to supply, in priority order: (1) the ownership boundary your PI will agree to for a side project — the single point of failure in §8, and the determinant of whether the independence narrative holds; (2) your visa/immigration status, which decides whether the US route retains any meaning (K99 effectively closed, F32 requires citizenship/permanent residency) and sets the clock on the Asian route; (3) a real inventory of unpublished data — you previously stated there is none on the ZSWIM8 line, but data elsewhere would reshape the Q1–Q2 schedule; (4) whether the banked MYBPC3 heart and SAA3 gut tissues still exist and who controls them, on which the "zero-cost start" of Direction 2 entirely depends; (5) a teaching/mentoring record, required for faculty applications and currently absent; (6) exact age and months-since-PhD, since the Asian schemes have hard ceilings; (7) a referee list with their willingness confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>One direct CV recommendation: delete the final ADDITIONAL / Certifications line (advanced nutritionist, psychological counsellor, kindergarten principal, paediatric massage). In a faculty or fellowship review it adds no credibility and invites a question about divided attention. Those certificates have value elsewhere — not on this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>11 · 双语输出说明 / Note on Bilingual Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>本报告各节均为中文在前、英文在后。表格采用中英双语表头与双语单元格，只列一份，而非同一张表重复中英两遍——这是对「双语输出」要求的一处有意压缩，目的是让表格可读；如需完全分离的中英两份文件，说一声即可生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
           <t>Each section is presented Chinese first, English second. Tables use bilingual headers and bilingual cells and appear once rather than being duplicated in each language — a deliberate compression of the bilingual requirement in favour of readability. Fully separated Chinese-only and English-only versions can be generated on request.</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>12 · 各方向完整立项书 / Full Proposals for Every Viable Direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>本节完整内容亦单独成文：proposals_all_directions.md。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>五个可行方向的完整立项书 / Full Proposals for All Viable Directions</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Xiaodong ZOU · 2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>统一叙事 / Unifying thesis</t>
         </is>
       </c>
     </row>
@@ -1760,23 +1753,31 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>代谢与信号状态如何通过控制 miRNA 的降解与末端修饰，决定慢性疾病的可逆性。 How metabolic and signalling state, acting through miRNA decay and 3′-end modification, sets the reversibility of chronic disease.</t>
+          <t>本节完整内容亦单独成文：proposals_all_directions.md。</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>五个方向共用 miR-29 作为核心 miRNA、共用一套方法栈（smallRNA-seq + 半衰期测定 + 编辑 + 类器官），所以它们可以作为同一份申请书的 Aims，而不是五个互相稀释的项目。</t>
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>五个可行方向的完整立项书 / Full Proposals for All Viable Directions</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>证据等级标注 / Evidence grading — 本文件每条机制前提都标注来源： [已发表] 有 PMID 支撑 · [本项目计算] 来自自建 PSSM，假设生成级 · [待测] 尚无证据。 所有图与数字若出现在申请书中，一律标注 predicted/schematic。</t>
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Xiaodong ZOU · 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1784,43 +1785,31 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>已识别的竞争风险（两篇，2026）</t>
+          <t>统一叙事 / Unifying thesis</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>方向 1 · AMPK–ZSWIM8–代谢记忆（旗舰）</t>
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>代谢与信号状态如何通过控制 miRNA 的降解与末端修饰，决定慢性疾病的可逆性。 How metabolic and signalling state, acting through miRNA decay and 3′-end modification, sets the reversibility of chronic disease.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Direction 1 · Energy stress → ZSWIM8 → metabolic memory</t>
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>五个方向共用 miR-29 作为核心 miRNA、共用一套方法栈（smallRNA-seq + 半衰期测定 + 编辑 + 类器官），所以它们可以作为同一份申请书的 Aims，而不是五个互相稀释的项目。</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>1.1 一句话假设</t>
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>证据等级标注 / Evidence grading — 本文件每条机制前提都标注来源： [已发表] 有 PMID 支撑 · [本项目计算] 来自自建 PSSM，假设生成级 · [待测] 尚无证据。 所有图与数字若出现在申请书中，一律标注 predicted/schematic。</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1817,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>能量应激激活的 AMPK 磷酸化 ZSWIM8，加速代谢相关 miRNA 的靶标导向降解（TDMD），把一过性代谢刺激固化为持久的「代谢记忆」。</t>
+          <t>已识别的竞争风险（两篇，2026）</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1829,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>1.2 科学前提</t>
+          <t>方向 1 · AMPK–ZSWIM8–代谢记忆（旗舰）</t>
         </is>
       </c>
     </row>
@@ -1852,15 +1841,19 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>1.3 Aim 1 — AMPK 是否直接磷酸化 ZSWIM8（12 个月 go/no-go）</t>
+          <t>Direction 1 · Energy stress → ZSWIM8 → metabolic memory</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>实验</t>
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1.1 一句话假设</t>
         </is>
       </c>
     </row>
@@ -1868,23 +1861,31 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>· 体外激酶反应：重组 AMPK（α1β1γ1）+ 纯化 ZSWIM8 片段（含 S608/S609 的无序区，约 560–660 aa），WT vs S608A vs S609A vs 双突变。必须同板跑经典 AMPK 底物肽作阳性对照（否则阴性结果无信息量，PMID 11902845）。</t>
+          <t>能量应激激活的 AMPK 磷酸化 ZSWIM8，加速代谢相关 miRNA 的靶标导向降解（TDMD），把一过性代谢刺激固化为持久的「代谢记忆」。</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>· Phos-tag SDS-PAGE 定量多位点磷酸化化学计量比——S608 在无序区，正是 Phos-tag 适用场景（PMID 32696389）。</t>
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1.2 科学前提</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>· 质谱定位位点：送 MSKCC proteomics core；位点定位概率阈值 &gt;0.75 方可作结论（PMID 27667718）。</t>
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Aim 1 — AMPK 是否直接磷酸化 ZSWIM8（12 个月 go/no-go）</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1893,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>· 细胞内验证：AICAR 与 A-769662（两种机制不同的激动剂互为对照）+ 葡萄糖剥夺；自制 phospho-S608 抗体检测；AMPKα1/α2 双敲除细胞作遗传对照。</t>
+          <t>实验</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1901,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>· 自制抗体：用你的杂交瘤能力做 phospho-ZSWIM8(S608) 单抗，按 PMID 15728188 的验证范式（磷酸酶处理 + 位点突变体双阴性对照）。</t>
+          <t>· 体外激酶反应：重组 AMPK（α1β1γ1）+ 纯化 ZSWIM8 片段（含 S608/S609 的无序区，约 560–660 aa），WT vs S608A vs S609A vs 双突变。必须同板跑经典 AMPK 底物肽作阳性对照（否则阴性结果无信息量，PMID 11902845）。</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1909,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>预期结果（predicted/schematic） WT + AMP 激活 ≈100%，WT 未激活 ≈44%，S608A ≈9%，无激酶 ≈6%，SAMS 阳性对照 ≈92%。</t>
+          <t>· Phos-tag SDS-PAGE 定量多位点磷酸化化学计量比——S608 在无序区，正是 Phos-tag 适用场景（PMID 32696389）。</t>
         </is>
       </c>
     </row>
@@ -1916,19 +1917,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>陷阱与替代 ① 全长 ZSWIM8（1837 aa）表达困难 → 用片段，但须在细胞内用全长回补验证。② 无序区片段易降解 → 加 MBP/SUMO 标签与蛋白酶抑制剂。③ 若 AMPK 不直接磷酸化 → 检查是否经 SIK/MARK 等 AMPK 家族激酶，或经中间体。</t>
+          <t>· 质谱定位位点：送 MSKCC proteomics core；位点定位概率阈值 &gt;0.75 方可作结论（PMID 27667718）。</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>1.4 Aim 2 — 磷酸化是否改变 miRNA 半衰期</t>
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>· 细胞内验证：AICAR 与 A-769662（两种机制不同的激动剂互为对照）+ 葡萄糖剥夺；自制 phospho-S608 抗体检测；AMPKα1/α2 双敲除细胞作遗传对照。</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1933,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>实验</t>
+          <t>· 自制抗体：用你的杂交瘤能力做 phospho-ZSWIM8(S608) 单抗，按 PMID 15728188 的验证范式（磷酸酶处理 + 位点突变体双阴性对照）。</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1941,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>· 半衰期测定：actinomycin D chase + smallRNA-seq，先在已知短命 miRNA 上做阳性对照再上候选（基准数值取自 PMID 31519739、方法取自 PMID 21447562）。</t>
+          <t>预期结果（predicted/schematic） WT + AMP 激活 ≈100%，WT 未激活 ≈44%，S608A ≈9%，无激酶 ≈6%，SAMS 阳性对照 ≈92%。</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1949,19 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>· 正交方法：4sU 代谢标记 / SLAM-seq 思路（PMID 28945705）——单一方法的偏倚必须用第二种方法排除。</t>
+          <t>陷阱与替代 ① 全长 ZSWIM8（1837 aa）表达困难 → 用片段，但须在细胞内用全长回补验证。② 无序区片段易降解 → 加 MBP/SUMO 标签与蛋白酶抑制剂。③ 若 AMPK 不直接磷酸化 → 检查是否经 SIK/MARK 等 AMPK 家族激酶，或经中间体。</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>· 内源位点突变：用你的 ABE/BE4 在内源位点敲入 S608A（磷酸化缺陷）与 S608D（拟磷酸化），不用过表达质粒——审稿人对内源点突变的信任度远高于过表达（可行性见 PMID 31937940 / 31634902 / 33606977）。</t>
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1.4 Aim 2 — 磷酸化是否改变 miRNA 半衰期</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1969,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>· 候选 miRNA：miR-29（抗纤维化）、miR-33（胆固醇/AMPK 轴）、miR-375（胰岛）；miR-375 的功能依据见 PMID 15538371。</t>
+          <t>实验</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1977,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>· AGO-RIP 检查载荷变化（Halo 增强法比 iCLIP 可行，PMID 32497496）。</t>
+          <t>· 半衰期测定：actinomycin D chase + smallRNA-seq，先在已知短命 miRNA 上做阳性对照再上候选（基准数值取自 PMID 31519739、方法取自 PMID 21447562）。</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1985,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>预期结果（predicted/schematic） 降解速率 S608D &gt; WT &gt; S608A &gt; ZSWIM8-KO（k ≈ 0.075 / 0.045 / 0.020 / 0.006 h⁻¹）。</t>
+          <t>· 正交方法：4sU 代谢标记 / SLAM-seq 思路（PMID 28945705）——单一方法的偏倚必须用第二种方法排除。</t>
         </is>
       </c>
     </row>
@@ -1992,19 +1993,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>陷阱与替代 ① Act-D 本身扰动细胞 → 限制在 8 小时内并用 4sU 正交。② 半衰期差异可能被归一化方式掩盖 → 预先固定 spike-in 归一化方案并写进 SOP。③ 若半衰期不变但载荷变化 → 假设改为「磷酸化调控 AGO2 载荷而非降解速率」，方向不废。</t>
+          <t>· 内源位点突变：用你的 ABE/BE4 在内源位点敲入 S608A（磷酸化缺陷）与 S608D（拟磷酸化），不用过表达质粒——审稿人对内源点突变的信任度远高于过表达（可行性见 PMID 31937940 / 31634902 / 33606977）。</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>1.5 Aim 3 — 在代谢记忆模型里验证因果</t>
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>· 候选 miRNA：miR-29（抗纤维化）、miR-33（胆固醇/AMPK 轴）、miR-375（胰岛）；miR-375 的功能依据见 PMID 15538371。</t>
         </is>
       </c>
     </row>
@@ -2012,39 +2009,35 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>实验 高糖脉冲后撤除 → 追踪 miR-29/33/375 丰度与靶基因随时间恢复 → 比较 WT / S608A / S608D / ZSWIM8-KO 的「记忆强度」；体系用类器官（你已有）与 T2D 小型猪样本（你自己的一作模型，PMID 见 CV #11）。 预期结果（predicted/schematic） 撤除后第 7 天：WT 恢复到 58%、KO 92%、S608A 88%（即失去记忆）。 陷阱 猪样本可及性未确认 → 主线放在类器官，猪作为加分验证。</t>
+          <t>· AGO-RIP 检查载荷变化（Halo 增强法比 iCLIP 可行，PMID 32497496）。</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>预期结果（predicted/schematic） 降解速率 S608D &gt; WT &gt; S608A &gt; ZSWIM8-KO（k ≈ 0.075 / 0.045 / 0.020 / 0.006 h⁻¹）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>陷阱与替代 ① Act-D 本身扰动细胞 → 限制在 8 小时内并用 4sU 正交。② 半衰期差异可能被归一化方式掩盖 → 预先固定 spike-in 归一化方案并写进 SOP。③ 若半衰期不变但载荷变化 → 假设改为「磷酸化调控 AGO2 载荷而非降解速率」，方向不废。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>1.6 可行性：为什么是你</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>1.7 时间线 · 目标产出 · 放弃条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>· 0–12 月：Aim 1 go/no-go + Aim 2 首批半衰期数据；抗体进入免疫程序（周期长，Q2 就要启动）。</t>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1.5 Aim 3 — 在代谢记忆模型里验证因果</t>
         </is>
       </c>
     </row>
@@ -2052,23 +2045,31 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>· 12–18 月：第一篇机制论文投稿（*Nucleic Acids Research* / *Cell Reports* / *EMBO J*）。</t>
+          <t>实验 高糖脉冲后撤除 → 追踪 miR-29/33/375 丰度与靶基因随时间恢复 → 比较 WT / S608A / S608D / ZSWIM8-KO 的「记忆强度」；体系用类器官（你已有）与 T2D 小型猪样本（你自己的一作模型，PMID 见 CV #11）。 预期结果（predicted/schematic） 撤除后第 7 天：WT 恢复到 58%、KO 92%、S608A 88%（即失去记忆）。 陷阱 猪样本可及性未确认 → 主线放在类器官，猪作为加分验证。</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>· 3 年：冲 *Molecular Cell* / *Genes &amp; Development*。</t>
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1.6 可行性：为什么是你</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>· 基金：海外优青 / NIH R01（NIDDK 而非 NCI）/ 香港 RGC ECS / 新加坡 NRF。</t>
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1.7 时间线 · 目标产出 · 放弃条件</t>
         </is>
       </c>
     </row>
@@ -2076,43 +2077,31 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>· 放弃条件（12 个月硬线）：若 (a) 体外激酶反应测不到磷酸化（阳性对照成立的前提下）且 (b) 任何代谢处理都不改变任何候选 miRNA 的半衰期 → 放弃「AMPK 直接磷酸化」，退守方向 2，并把代谢输入层从翻译后修饰改为转录/翻译调控。</t>
+          <t>· 0–12 月：Aim 1 go/no-go + Aim 2 首批半衰期数据；抗体进入免疫程序（周期长，Q2 就要启动）。</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>方向 2 · TUT4/7–miR-29 纤维化检查点（最快出成果）</t>
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>· 12–18 月：第一篇机制论文投稿（*Nucleic Acids Research* / *Cell Reports* / *EMBO J*）。</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Direction 2 · Uridylation checkpoint on anti-fibrotic miRNA</t>
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>· 3 年：冲 *Molecular Cell* / *Genes &amp; Development*。</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>2.1 一句话假设</t>
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>· 基金：海外优青 / NIH R01（NIDDK 而非 NCI）/ 香港 RGC ECS / 新加坡 NRF。</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2109,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>器官纤维化时，TUT4/7 对 miR-29 的 3′ 尿苷化加速其降解，解除对胶原的抑制；这个开关可药控。</t>
+          <t>· 放弃条件（12 个月硬线）：若 (a) 体外激酶反应测不到磷酸化（阳性对照成立的前提下）且 (b) 任何代谢处理都不改变任何候选 miRNA 的半衰期 → 放弃「AMPK 直接磷酸化」，退守方向 2，并把代谢输入层从翻译后修饰改为转录/翻译调控。</t>
         </is>
       </c>
     </row>
@@ -2132,15 +2121,19 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>2.2 科学前提 —— 以及一个必须正面处理的竞争解释</t>
+          <t>方向 2 · TUT4/7–miR-29 纤维化检查点（最快出成果）</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>这一条决定方向 2 成立与否，必须写进申请书正面回应： 既然 TGF-β/Smad3 已在转录层解释了 miR-29 下降，我的第一个实验就不是测成熟体，而是测 pri/pre-miR-29 与成熟体的比值。若前体同步下降 → 转录机制主导，假设降级；若前体不变而成熟体下降 → 降解/加工层被打开，假设成立。这是一个真正的 go/no-go，而不是一个必然成功的实验。</t>
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Direction 2 · Uridylation checkpoint on anti-fibrotic miRNA</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2145,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>2.3 Aim 1 — 区分转录 vs 降解（零成本起步，9 个月内可完成）</t>
+          <t>2.1 一句话假设</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2153,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>实验 在你已发表的两个模型的存档组织上：① qPCR 测 pri-/pre-/成熟 miR-29a/b/c 三层；② 小 RNA 3′ 末端测序（TAIL-seq 思路，PMID 24582499）测尿苷化比例；③ 与纤维化程度（胶原定量）做相关。 体系：MYBPC3 缺失心脏（CV #7）+ SAA3 缺失 DSS-IBD 肠（CV #5）——两个不同器官，同一逻辑，这是几乎无人具备的对照。</t>
+          <t>器官纤维化时，TUT4/7 对 miR-29 的 3′ 尿苷化加速其降解，解除对胶原的抑制；这个开关可药控。</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2165,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>2.4 Aim 2 — TUT4/7 是否是执行者</t>
+          <t>2.2 科学前提 —— 以及一个必须正面处理的竞争解释</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2173,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>实验 TUT4/TUT7 单敲与双敲（siRNA + ASO 两种方式互为对照）→ miR-29 末端状态与半衰期 → 胶原读出；DIS3L2 敲低验证下游；类器官纤维化模型复现（模型依据 PMID 25828392）。 关键对照 必须同时检验「加工层 vs 降解层」：若 TUT4/7 敲低同时改变前体加工，则效应不能归因于降解（依据 P4 的反例）。</t>
+          <t>这一条决定方向 2 成立与否，必须写进申请书正面回应： 既然 TGF-β/Smad3 已在转录层解释了 miR-29 下降，我的第一个实验就不是测成熟体，而是测 pri/pre-miR-29 与成熟体的比值。若前体同步下降 → 转录机制主导，假设降级；若前体不变而成熟体下降 → 降解/加工层被打开，假设成立。这是一个真正的 go/no-go，而不是一个必然成功的实验。</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2185,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>2.5 Aim 3 — 可药控性</t>
+          <t>2.3 Aim 1 — 区分转录 vs 降解（零成本起步，9 个月内可完成）</t>
         </is>
       </c>
     </row>
@@ -2200,27 +2193,27 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>实验 ASO 阻断 miR-29 的尿苷化位点 / TUT4-7 抑制剂（若可得）→ 纤维化消退读出；人源验证用狭窄型克罗恩病样本的分子标记对齐（PMID 42622514），病理亚群参照 TWIST1⁺FAP⁺ 成纤维细胞（PMID 39024569）。 临床语境 IBD 纤维化的未满足需求与终点取自 PMID 27720839（*Gastroenterology* 综述）；心、肠纤维化目前零获批药——这是 Significance 的核心数字。</t>
+          <t>实验 在你已发表的两个模型的存档组织上：① qPCR 测 pri-/pre-/成熟 miR-29a/b/c 三层，三个成员分开做、不合并（依据 P6：成员间丰度差 5–14 倍）；② 小 RNA 3′ 末端测序（TAIL-seq 思路，PMID 24582499）测尿苷化比例；③ 与纤维化程度（胶原定量）做相关。</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>这个 Aim 的定量门槛（读完全文后才定得下来）：转录路线在系膜细胞里给出的成熟体降幅是 28–46%（PMID 22095944）。所以我的判据不能只看「成熟体是否下降」，而要看前体/成熟体比值是否偏离：若成熟体降 ~30–45% 且前体同步等比下降 → 落在转录解释的射程内，假设降级；若前体不变或降幅明显小于成熟体 → 降解/加工层被打开。样本量按最低丰度成员（miR-29b）估，不按 miR-29a。 体系：MYBPC3 缺失心脏（CV #7）+ SAA3 缺失 DSS-IBD 肠（CV #5）——两个不同器官，同一逻辑，这是几乎无人具备的对照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>2.6 时间线 · 目标产出 · 放弃条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>· 0–9 月：Aim 1 完成（存档样本，启动成本接近零）。</t>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Aim 2 — TUT4/7 是否是执行者</t>
         </is>
       </c>
     </row>
@@ -2228,15 +2221,19 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>· 9–12 月：第一篇投稿（*JCI Insight* / *Cell Death &amp; Disease* / 消化或心血管专业刊）。</t>
+          <t>实验 TUT4/TUT7 单敲与双敲（siRNA + ASO 两种方式互为对照）→ miR-29 末端状态与半衰期 → 胶原读出；DIS3L2 敲低验证下游；类器官纤维化模型复现（模型依据 PMID 25828392）。 关键对照 必须同时检验「加工层 vs 降解层」：若 TUT4/7 敲低同时改变前体加工，则效应不能归因于降解（依据 P4 的反例）。</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>· 定位：这是「保产出、养实验室」的现金流方向，与方向 1 的高风险互补。</t>
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Aim 3 — 可药控性</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2241,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>· 放弃条件：两个器官模型都测不到末端修饰差异，且前体同步下降 → 转向「miR-29 丰度的其他调控机制（AGO 载荷 / TDMD 触发转录本）」，或把资源并入方向 1。</t>
+          <t>实验 ASO 阻断 miR-29 的尿苷化位点 / TUT4-7 抑制剂（若可得）→ 纤维化消退读出；人源验证用狭窄型克罗恩病样本的分子标记对齐（PMID 39977234：81 个重叠 DEG，GREM1／SERPINE1／LY96 为狭窄特异候选，GREM1 经 scRNA-seq 定位于成纤维细胞；⚠️ 该研究无健康对照、无功能学验证，这些基因只是关联标志，只能用作对齐坐标、不能当已验证 biomarker 写。原计划引的 PMID 42622514 无开放全文），病理亚群参照 TWIST1⁺FAP⁺ 成纤维细胞（PMID 39024569）。 临床语境 IBD 纤维化的未满足需求与终点取自 PMID 27720839（*Gastroenterology* 综述）；心、肠纤维化目前零获批药——这是 Significance 的核心数字。</t>
         </is>
       </c>
     </row>
@@ -2256,31 +2253,23 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>方向 3 · 乳酸/乳酰化对小 RNA 稳态的调控（身份标签）</t>
+          <t>2.6 时间线 · 目标产出 · 放弃条件</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>Direction 3 · Lactate &amp; lactylation as an input to small-RNA homeostasis</t>
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>· 0–9 月：Aim 1 完成（存档样本，启动成本接近零）。</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>3.1 一句话假设</t>
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>· 9–12 月：第一篇投稿（*JCI Insight* / *Cell Death &amp; Disease* / 消化或心血管专业刊）。</t>
         </is>
       </c>
     </row>
@@ -2288,27 +2277,27 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>乳酸及蛋白乳酰化直接修饰 AGO2 / ZSWIM8 / TUT4-7，重编程 miRNA 稳态。</t>
+          <t>· 定位：这是「保产出、养实验室」的现金流方向，与方向 1 的高风险互补。</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>· 放弃条件：两个器官模型都测不到末端修饰差异，且前体同步下降 → 转向「miR-29 丰度的其他调控机制（AGO 载荷 / TDMD 触发转录本）」，或把资源并入方向 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>3.2 科学前提 —— 先例已经存在，而且是 RNA 酶</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>为什么是你：你有一作论文完整证明「乳酸 → 胆固醇合成 → 病毒复制」的因果链（PMID 见 CV #8），乳酸是你手上的现成工具而非新学的技术。全世界同时具备「乳酸因果链经验 + miRNA 降解机器语境」的人极少。</t>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>方向 3 · 乳酸/乳酰化对小 RNA 稳态的调控（身份标签）</t>
         </is>
       </c>
     </row>
@@ -2320,15 +2309,19 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>3.3 三个 Aim（压缩版）</t>
+          <t>Direction 3 · Lactate &amp; lactylation as an input to small-RNA homeostasis</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>· Aim 1 乳酸处理 / 糖酵解抑制 → AGO2、ZSWIM8、TUT4/7 免疫沉淀 + 泛乳酰化 western 筛查。</t>
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>3.1 一句话假设</t>
         </is>
       </c>
     </row>
@@ -2336,35 +2329,39 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>· Aim 2 质谱定位乳酰化位点（必需质谱合作者）→ 用你的碱基编辑在内源位点做位点突变（K→R 去修饰、K→Q 拟修饰）→ 测 miRNA 半衰期。</t>
+          <t>乳酸及蛋白乳酰化直接修饰 AGO2 / ZSWIM8 / TUT4-7，重编程 miRNA 稳态。</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>· Aim 3 在你的疾病体系里验证：乳酸高的微环境（炎症肠、缺血心肌）是否对应 miRNA 稳态改变。</t>
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>3.2 科学前提 —— 先例已经存在，而且是 RNA 酶</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="inlineStr">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>为什么是你：你有一作论文完整证明「乳酸 → 胆固醇合成 → 病毒复制」的因果链（PMID 见 CV #8），乳酸是你手上的现成工具而非新学的技术。全世界同时具备「乳酸因果链经验 + miRNA 降解机器语境」的人极少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>3.4 定位 · 风险 · 放弃条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>· 建议先作为方向 1 主基金里的 Aim 3，或申请探索性/种子基金，不要一开始就独立立项。</t>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>3.3 三个 Aim（压缩版）</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2369,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>· 时间线 18–30 个月；高风险高回报。</t>
+          <t>· Aim 1 乳酸处理 / 糖酵解抑制 → AGO2、ZSWIM8、TUT4/7 免疫沉淀 + 泛乳酰化 western 筛查。</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2377,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>· 风险 乳酰化可能只是间接效应（经 pH 或代谢通量改变）——必须做 pH 匹配对照与非代谢性酸化对照。</t>
+          <t>· Aim 2 质谱定位乳酰化位点（必需质谱合作者）→ 用你的碱基编辑在内源位点做位点突变（K→R 去修饰、K→Q 拟修饰）→ 测 miRNA 半衰期。</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2385,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>· 放弃条件 若位点突变不改变 miRNA 半衰期 → 降级为方向 1 的补充 Aim，不独立立项。</t>
+          <t>· Aim 3 在你的疾病体系里验证：乳酸高的微环境（炎症肠、缺血心肌）是否对应 miRNA 稳态改变。</t>
         </is>
       </c>
     </row>
@@ -2400,31 +2397,23 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>方向 4 · 类器官 TDMD 报告平台（资源/合作牌）</t>
+          <t>3.4 定位 · 风险 · 放弃条件</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>Direction 4 · An organoid TDMD reporter platform</t>
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>· 建议先作为方向 1 主基金里的 Aim 3，或申请探索性/种子基金，不要一开始就独立立项。</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>4.1 一句话目标</t>
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>· 时间线 18–30 个月；高风险高回报。</t>
         </is>
       </c>
     </row>
@@ -2432,63 +2421,71 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" s="3" t="inlineStr">
         <is>
+          <t>· 风险 乳酰化可能只是间接效应（经 pH 或代谢通量改变）——必须做 pH 匹配对照与非代谢性酸化对照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>· 放弃条件 若位点突变不改变 miRNA 半衰期 → 降级为方向 1 的补充 Aim，不独立立项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>方向 4 · 类器官 TDMD 报告平台（资源/合作牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Direction 4 · An organoid TDMD reporter platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>4.1 一句话目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
           <t>建立疾病特异的类器官 + TDMD 荧光报告系统，把 miRNA 降解动态变成可定量、可筛选的活体读出。</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>4.2 前提与空白</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>· 类器官已可用于抗纤维化药评价 [已发表] PMID 25828392；操作方案 PMID 42763855。</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr"/>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>· TDMD 极少在类器官/大动物层面做因果验证 [待测] —— 现有工作基本止于细胞系（对比 PMID 37532519、29887379）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr"/>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>· 体内 miRNA 靶标鉴定已有比 iCLIP 更可行的方法 [已发表] PMID 32497496。</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>4.3 三个 Aim</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>· Aim 1 构建 TDMD 荧光报告（双色比值读出：报告 miRNA vs 对照 miRNA），用内源位点敲入而非质粒，降低批次噪声。</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2493,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>· Aim 2 移植进你已有的肠类器官与纤维化读出体系，标定动态范围与批次变异（类器官定量标准化是公认弱点，必须自己给出 CV%）。</t>
+          <t>· 类器官已可用于抗纤维化药评价 [已发表] PMID 25828392；操作方案 PMID 42763855。</t>
         </is>
       </c>
     </row>
@@ -2504,139 +2501,135 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
+          <t>· TDMD 极少在类器官/大动物层面做因果验证 [待测] —— 现有工作基本止于细胞系（对比 PMID 37532519、29887379）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>· 体内 miRNA 靶标鉴定已有比 iCLIP 更可行的方法 [已发表] PMID 32497496。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>4.3 三个 Aim</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>· Aim 1 构建 TDMD 荧光报告（双色比值读出：报告 miRNA vs 对照 miRNA），用内源位点敲入而非质粒，降低批次噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>· Aim 2 移植进你已有的肠类器官与纤维化读出体系，标定动态范围与批次变异（类器官定量标准化是公认弱点，必须自己给出 CV%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
           <t>· Aim 3 小规模化合物/遗传筛选，产出「能改变 miRNA 半衰期的干预清单」。</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="1" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>4.4 定位</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr"/>
-      <c r="B217" s="3" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>不作为独立学术主线，而是「资源牌」：平台成果易发方法学论文、易与临床和药企谈合作、易拿平台类经费，适合作为 PI 起步的谈判资本。风险是平台易被复制——差异化必须落在独特读出 + 你自己的疾病模型，而不是「我们也做类器官」。</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="1" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>方向 5 · 碱基编辑解剖 TDMD 的功能语法（方法学手术刀）</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="1" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>Direction 5 · Dissecting the TDMD grammar by base editing</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="1" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>5.1 一句话目标</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr"/>
-      <c r="B221" s="3" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" s="3" t="inlineStr">
         <is>
           <t>在内源位点逐个敲入/破坏磷酸化位点与底物识别位点，解析 ZSWIM8 决定「降解谁、何时降解」的功能语法。</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="1" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>5.2 前提</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" s="3" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>· Prime editing 与碱基编辑可在内源位点高效引入点突变 [已发表] PMID 31634902 / 31937940；规模化变异评估范式 PMID 33606977。</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr"/>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>· ZSWIM8 的底物识别语法未解 [待测]；结构约束见 PMID 41851464、31353209。</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>· 竞争提示：PMID 41542392（2026 预印本）正在做 TDMD 特异性机制——本方向必须与其划清界线，或转为合作。</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>5.3 定位</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>作为方向 1/3 的机制手术刀，不独立立项。 它的价值是让方向 1 的关键结论建立在内源位点突变而非过表达之上——这一点对审稿人极重要，而多数 RNA 实验室做不到，你能做。</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>五方向决策表 / Decision matrix</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2637,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>组合建议：1 + 2 为双主线（一高新颖度、一快产出，共用 miR-29 叙事），3 作为 1 的 Aim 3 用来在申请书里凸显「只有我能做」，4/5 写进每个 Aim 的可行性段落。</t>
+          <t>· ZSWIM8 的底物识别语法未解 [待测]；结构约束见 PMID 41851464、31353209。</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2645,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>明确退出：胃癌 lncRNA-Wnt 线（VAX2/SNHG9、Linc01189、Linc02139）与「兽医病毒」作为独立方向——理由见主报告第 4/5 节。</t>
+          <t>· 竞争提示：PMID 41542392（2026 预印本）正在做 TDMD 特异性机制——本方向必须与其划清界线，或转为合作。</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2657,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>English summary</t>
+          <t>5.3 定位</t>
         </is>
       </c>
     </row>
@@ -2672,15 +2665,19 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Five proposals under one thesis: metabolic and signalling state controlling miRNA decay and 3′-end modification, and thereby the reversibility of chronic disease. Every mechanistic premise is graded [published] with a PMID, [computed in this project] (the AMPK PSSM — hypothesis-generating only, the score is not evidence), or [untested].</t>
+          <t>作为方向 1/3 的机制手术刀，不独立立项。 它的价值是让方向 1 的关键结论建立在内源位点突变而非过表达之上——这一点对审稿人极重要，而多数 RNA 实验室做不到，你能做。</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>Direction 1 (flagship) — AMPK phosphorylates ZSWIM8 to accelerate TDMD of metabolic miRNAs, converting transient metabolic insult into durable memory. Aim 1 is a 12-month go/no-go: in-vitro kinase assay on recombinant disordered-region fragments (WT vs S→A) with a canonical AMPK substrate on the same gel, Phos-tag stoichiometry, MS site localisation above 0.75 probability, and cellular validation with two mechanistically distinct AMPK agonists plus AMPKα1/α2 double knockout. Aim 2 measures half-life by Act-D chase plus an orthogonal 4sU/SLAM-seq approach, with S608A/S608D installed at the endogenous locus by base editing rather than overexpression. Aim 3 tests memory strength after a glucose pulse in organoids and T2D pig material. Explicit abandonment condition at 12 months with a named fallback.</t>
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>五方向决策表 / Decision matrix</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2685,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Direction 2 (fastest) — TUT4/7 uridylation of miR-29 as a druggable fibrosis checkpoint, startable on banked tissue from his own two published organ models at near-zero cost. Crucially, the literature already offers a strong competing explanation: TGF-β/Smad3 suppresses miR-29 transcriptionally (PMID 21784902, 22095944). The proposal therefore makes its first experiment the pri/pre-versus-mature ratio, which discriminates the two mechanisms — a genuine go/no-go rather than a guaranteed result. It must also separate the processing layer from the decay layer, because uridylation is known to *promote* processing in other contexts (PMID 23063654, 39054354).</t>
+          <t>组合建议：1 + 2 为双主线（一高新颖度、一快产出，共用 miR-29 叙事），3 作为 1 的 Aim 3 用来在申请书里凸显「只有我能做」，4/5 写进每个 Aim 的可行性段落。</t>
         </is>
       </c>
     </row>
@@ -2696,15 +2693,19 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Direction 3 (identity marker) — lactate/lactylation as an input to the small-RNA machinery. Precedent is real and recent: lactylation of the RNA-modifying enzymes METTL3 and METTL16 changes their function (PMID 35320754, 37863889), and AARS1 is an established lactate sensor and lactyltransferase (PMID 38653238). No report of lactate acting on the miRNA decay machinery appeared in a 632-paper candidate pool — a genuine gap. Requires a mass-spectrometry collaborator; run it as Aim 3 of Direction 1, not standalone, and control for pH and non-metabolic acidification.</t>
+          <t>明确退出：胃癌 lncRNA-Wnt 线（VAX2/SNHG9、Linc01189、Linc02139）与「兽医病毒」作为独立方向——理由见主报告第 4/5 节。</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>Direction 4 — an organoid TDMD reporter platform: a resource and collaboration asset rather than an academic identity, differentiated by unique read-out plus his own disease models, with batch CV% reported honestly.</t>
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>English summary</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2713,7 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Direction 5 — base editing to dissect the TDMD grammar at endogenous loci: the mechanistic scalpel that lets Direction 1's key claims rest on endogenous point mutants rather than overexpression, which most RNA labs cannot do.</t>
+          <t>Five proposals under one thesis: metabolic and signalling state controlling miRNA decay and 3′-end modification, and thereby the reversibility of chronic disease. Every mechanistic premise is graded [published] with a PMID, [computed in this project] (the AMPK PSSM — hypothesis-generating only, the score is not evidence), or [untested].</t>
         </is>
       </c>
     </row>
@@ -2720,19 +2721,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Recommended combination: 1 + 2 as twin core lines sharing the miR-29 narrative, 3 as Aim 3 for differentiation, 4/5 in the feasibility paragraphs. Deliberately exit the lncRNA gastric-cancer line and veterinary virology as standalone directions.</t>
+          <t>Direction 1 (flagship) — AMPK phosphorylates ZSWIM8 to accelerate TDMD of metabolic miRNAs, converting transient metabolic insult into durable memory. Aim 1 is a 12-month go/no-go: in-vitro kinase assay on recombinant disordered-region fragments (WT vs S→A) with a canonical AMPK substrate on the same gel, Phos-tag stoichiometry, MS site localisation above 0.75 probability, and cellular validation with two mechanistically distinct AMPK agonists plus AMPKα1/α2 double knockout. Aim 2 measures half-life by Act-D chase plus an orthogonal 4sU/SLAM-seq approach, with S608A/S608D installed at the endogenous locus by base editing rather than overexpression. Aim 3 tests memory strength after a glucose pulse in organoids and T2D pig material. Explicit abandonment condition at 12 months with a named fallback.</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>13 · 文献阅读计划（逐周）与论文记录模板 / Reading Plan &amp; Note Template</t>
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Direction 2 (fastest) — TUT4/7 uridylation of miR-29 as a druggable fibrosis checkpoint, startable on banked tissue from his own two published organ models at near-zero cost. Crucially, the literature already offers a strong competing explanation: TGF-β/Smad3 suppresses miR-29 transcriptionally (PMID 21784902, 22095944). The proposal therefore makes its first experiment the pri/pre-versus-mature ratio, which discriminates the two mechanisms — a genuine go/no-go rather than a guaranteed result. It must also separate the processing layer from the decay layer, because uridylation is known to *promote* processing in other contexts (PMID 23063654, 39054354).</t>
         </is>
       </c>
     </row>
@@ -2740,19 +2737,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>可执行工作簿：reading_plan_12weeks.xlsx（11 张表，含 4 本台账）；路线图：fig_reading_roadmap.png。</t>
+          <t>Direction 3 (identity marker) — lactate/lactylation as an input to the small-RNA machinery. Precedent is real and recent: lactylation of the RNA-modifying enzymes METTL3 and METTL16 changes their function (PMID 35320754, 37863889), and AARS1 is an established lactate sensor and lactyltransferase (PMID 38653238). No report of lactate acting on the miRNA decay machinery appeared in a 632-paper candidate pool — a genuine gap. Requires a mass-spectrometry collaborator; run it as Aim 3 of Direction 1, not standalone, and control for pH and non-metabolic acidification.</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>13.1 十二周总览 / Twelve-week overview</t>
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Direction 4 — an organoid TDMD reporter platform: a resource and collaboration asset rather than an academic identity, differentiated by unique read-out plus his own disease models, with batch CV% reported honestly.</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2753,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>每日 90 分钟阅读窗（回忆 10′ → 精读 45′ → 速读 20′ → 转译 10′ → 归档 5′）。这是相对结构而非固定钟点——把开始时间换成你自己的晨间块即可；若你把日程表给我，我可以按你的真实时间块重排。</t>
+          <t>Direction 5 — base editing to dissect the TDMD grammar at endogenous loci: the mechanistic scalpel that lets Direction 1's key claims rest on endogenous point mutants rather than overexpression, which most RNA labs cannot do.</t>
         </is>
       </c>
     </row>
@@ -2768,27 +2761,27 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>分层时间预算：T0 精读 ~60 min（26 篇）· T1 结构化速读 ~25 min（28 篇）· T2 略读 ~10 min（14 篇），共 68 篇，约 33 小时。候选池 632 篇（PubMed + Europe PMC 实时检索，见 reading_pool.csv）。</t>
+          <t>Recommended combination: 1 + 2 as twin core lines sharing the miR-29 narrative, 3 as Aim 3 for differentiation, 4/5 in the feasibility paragraphs. Deliberately exit the lncRNA gastric-cancer line and veterinary virology as standalone directions.</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr"/>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>两个不能跳的周：W7 处理 miR-29 的转录层替代解释（这是方向 2 的 go/no-go）；W12 逐句读 2026 年最接近的三篇（竞争风险）。</t>
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>13 · 文献阅读计划（逐周）与论文记录模板 / Reading Plan &amp; Note Template</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>13.2 每周论文清单（含为什么读 / 必须记下什么）</t>
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>可执行工作簿：reading_plan_12weeks.xlsx（11 张表，含 4 本台账）；路线图：fig_reading_roadmap.png。</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2793,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>W1 · TDMD 机制奠基：谁识别、谁泛素化、谁被降解</t>
+          <t>13.1 十二周总览 / Twelve-week overview</t>
         </is>
       </c>
     </row>
@@ -2808,19 +2801,15 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>本周问题： TDMD 的最小组件是什么？ZSWIM8 识别的是 miRNA 还是 AGO2 的构象？ 配套计算任务： 把 4 篇奠基文的模型画成一张机制图（自己画，不抄图） 配套实验准备： 订 ZSWIM8/AGO2 抗体目录号，查是否有可用 phospho 抗体（预期没有） 周末产出物： 一页手绘机制图 + 一句话写清「机器怎么工作」</t>
+          <t>每日 90 分钟阅读窗（回忆 10′ → 精读 45′ → 速读 20′ → 转译 10′ → 归档 5′）。这是相对结构而非固定钟点——把开始时间换成你自己的晨间块即可；若你把日程表给我，我可以按你的真实时间块重排。</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>W2 · 机器的边界、保护面与结构约束</t>
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>分层时间预算：T0 精读 ~60 min（26 篇）· T1 结构化速读 ~25 min（26 篇）· T2 略读 ~10 min（16 篇），共 68 篇，约 40 小时。候选池 632 篇（PubMed + Europe PMC 实时检索，见 reading_pool.csv）。</t>
         </is>
       </c>
     </row>
@@ -2828,27 +2817,27 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>本周问题： ZSWIM8 的底物特异性由什么决定？我预测的 S608/S609 在结构上可及吗？ 配套计算任务： 在 UniProt/AlphaFold 上标出 S608/S609 与 SWIM 域(172–208) 的相对位置 配套实验准备： 准备 ZSWIM8 片段表达构建（S608 所在无序区）的引物设计 周末产出物： 一页「已知 vs 未知」清单，圈出我要攻的那一格</t>
+          <t>2026-09-29：68 篇的 14 栏笔记已按全文预填，你是核对而不是从空白开始。 三篇替代文献（W6 的 41465114、W7 的 40124162、W9 的 39977234）层级判为 T2，因此 T1 由 28 减至 26、T2 由 14 增至 16——这是降级，不是等价替换；若你能用机构订阅取到原文，应恢复原层级并按原文重填。 预填稿见 paper_notes_68_fulltext.xlsx（28 列可筛选，按来源三色标注）。</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="inlineStr">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>两个不能跳的周：W7 处理 miR-29 的转录层替代解释（这是方向 2 的 go/no-go）；W12 逐句读 2026 年最接近的三篇（竞争风险）。 读完全文后 W7 的形势更紧，不是更松：转录路线已经有定位到上游 22 kb 的 Smad3 结合位点（PMID 21784902 Fig.3A）和 28%／46%／37% 的成员分辨降幅（PMID 22095944），而四篇里没有一篇测过前体——所以 W7 要交的决策备忘必须直接回答：我的前体/成熟体比值实验，能不能把降幅落在转录解释的射程之外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>W3 · 把「半衰期」变成可测量的数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>本周问题： 在我的体系里，一个 miRNA 的半衰期该怎么测、测到多少才算可信？ 配套计算任务： 下载一套公开 smallRNA-seq 数据，跑通定量与半衰期拟合 配套实验准备： 预约测序平台；准备 actinomycin D 与阳性对照（已知短命 miRNA） 周末产出物： 半衰期测定 SOP 草稿（含归一化方式与重复数）</t>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>13.2 每周论文清单（含为什么读 / 必须记下什么）</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2849,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>W4 · AMPK 底物识别语法——决定我的位点预测可不可信</t>
+          <t>W1 · TDMD 机制奠基：谁识别、谁泛素化、谁被降解</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2857,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>本周问题： AMPK 底物基序的真实判据是什么？我的 PSSM 打分够不够支持一个假设？ 配套计算任务： 用本项目自建 PSSM 复算这几篇里的已知底物，看能否复现它们的高分位 配套实验准备： 设计体外激酶反应：重组片段 + 经典底物肽阳性对照（同板） 周末产出物： 一页「S608 预测的证据强度自评」，明确写出它只是假设生成级</t>
+          <t>本周问题： TDMD 的最小组件是什么？ZSWIM8 识别的是 miRNA 还是 AGO2 的构象？ 配套计算任务： 把 4 篇奠基文的模型画成一张机制图（自己画，不抄图） 配套实验准备： 订 ZSWIM8/AGO2 抗体目录号，查是否有可用 phospho 抗体（预期没有） 周末产出物： 一页手绘机制图 + 一句话写清「机器怎么工作」</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2869,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>W5 · 信号 × miRNA：既有证据与反向因果的威胁</t>
+          <t>W2 · 机器的边界、保护面与结构约束</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2877,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 文献里 AMPK 与 miRNA 的关系，有多少是「miRNA 调控 AMPK」而不是反过来？ 配套计算任务： 把检索到的 AMPK–miRNA 论文按因果方向归类，统计两个方向各多少篇 配套实验准备： 联系质谱平台（磷酸化位点鉴定），问清送样要求与最低上样量 周末产出物： 一段「反向因果」辩护词：为什么我的方向不是已有文献的重复</t>
+          <t>本周问题： ZSWIM8 的底物特异性由什么决定？我预测的 S608/S609 在结构上可及吗？ 配套计算任务： 在 UniProt/AlphaFold 上标出 S608/S609 与 SWIM 域(172–208) 的相对位置 配套实验准备： 准备 ZSWIM8 片段表达构建（S608 所在无序区）的引物设计 周末产出物： 一页「已知 vs 未知」清单，圈出我要攻的那一格</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2889,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>W6 · 代谢记忆：疾病叙事与已有机制解释</t>
+          <t>W3 · 把「半衰期」变成可测量的数字</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2897,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 「代谢记忆」现有的机制解释是什么？miRNA 降解这一层有没有被占？ 配套计算任务： 把代谢记忆的既有机制画成分层图（转录/表观/代谢物/RNA），标出空白层 配套实验准备： T2D 猪与类器官样本清单盘点：还剩哪些、在谁手里 周末产出物： 申请书 Significance 段落初稿（一段，可直接用）</t>
+          <t>本周问题： 在我的体系里，一个 miRNA 的半衰期该怎么测、测到多少才算可信？ 配套计算任务： 下载一套公开 smallRNA-seq 数据，跑通定量与半衰期拟合 配套实验准备： 预约测序平台；准备 actinomycin D 与阳性对照（已知短命 miRNA） 周末产出物： 半衰期测定 SOP 草稿（含归一化方式与重复数）</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2909,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>W7 · 竞争风险周：miR-29 为什么被关掉——转录解释已经很强</t>
+          <t>W4 · AMPK 底物识别语法——决定我的位点预测可不可信</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2917,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 如果 TGF-β/Smad3 在转录层已经解释了 miR-29 下降，我的降解假设还剩多少空间？ 配套计算任务： 把四篇 miR-29 论文的效应量列成一张表（mRNA 降幅 vs 成熟体降幅） 配套实验准备： 在心/肠存档样本上先测 miR-29 前体 vs 成熟体比值（区分转录 vs 降解） 周末产出物： 一页决策备忘：我的方向 2 是否仍然成立（这是 go/no-go）</t>
+          <t>本周问题： AMPK 底物基序的真实判据是什么？我的 PSSM 打分够不够支持一个假设？ 配套计算任务： 用本项目自建 PSSM 复算这几篇里的已知底物，看能否复现它们的高分位 配套实验准备： 设计体外激酶反应：重组片段 + 经典底物肽阳性对照（同板） 周末产出物： 一页「S608 预测的证据强度自评」，明确写出它只是假设生成级</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2929,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>W8 · 尿苷化机器：TUT4/7 与 DIS3L2 的完整通路</t>
+          <t>W5 · 信号 × miRNA：既有证据与反向因果的威胁</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2937,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 尿苷化在什么条件下把一个 miRNA 送去降解，而不是改变它的加工？ 配套计算任务： 梳理 TUT4/7 底物特异性的已知规则，判断 miR-29 是否符合 配套实验准备： 订 TUT4/TUT7 敲低试剂（siRNA/ASO）与 DIS3L2 抗体 周末产出物： 方向 2 的实验设计图（含区分转录 vs 尿苷化的关键对照）</t>
+          <t>本周问题： 文献里 AMPK 与 miRNA 的关系，有多少是「miRNA 调控 AMPK」而不是反过来？ 配套计算任务： 把检索到的 AMPK–miRNA 论文按因果方向归类，统计两个方向各多少篇 配套实验准备： 联系质谱平台（磷酸化位点鉴定），问清送样要求与最低上样量 周末产出物： 一段「反向因果」辩护词：为什么我的方向不是已有文献的重复</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2949,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>W9 · 落点器官：肠狭窄与心脏纤维化的真实病理</t>
+          <t>W6 · 代谢记忆：疾病叙事与已有机制解释</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2957,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 我的两个器官模型，各自的临床终点与病理性成纤维细胞亚群是什么？ 配套计算任务： 把自己 MYBPC3 与 SAA3 两篇的表型与文献里的亚群标记对齐 配套实验准备： 设计类器官纤维化读出（胶原、硬度）的定量方案 周末产出物： 两器官对照表：共同机制 vs 器官特异机制，各写三条</t>
+          <t>本周问题： 「代谢记忆」现有的机制解释是什么？miRNA 降解这一层有没有被占？ 配套计算任务： 把代谢记忆的既有机制画成分层图（转录/表观/代谢物/RNA），标出空白层 配套实验准备： T2D 猪与类器官样本清单盘点：还剩哪些、在谁手里 周末产出物： 申请书 Significance 段落初稿（一段，可直接用）</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2969,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>W10 · 乳酰化：非组蛋白与 RNA 机器的既有先例</t>
+          <t>W7 · 竞争风险周：miR-29 为什么被关掉——转录解释已经很强</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2977,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 乳酸能否直接修饰 RNA 处理酶？已有先例的证据标准是什么？ 配套计算任务： 列出所有已报道的非组蛋白乳酰化底物，看有没有 RNA 结合蛋白 配套实验准备： 与质谱平台确认乳酰化位点鉴定的可行性与样本量 周末产出物： 方向 3 的可行性判断书：做 / 降级为 Aim3 / 不做（三选一，写理由）</t>
+          <t>本周问题： 如果 TGF-β/Smad3 在转录层已经解释了 miR-29 下降，我的降解假设还剩多少空间？ 配套计算任务： 把四篇 miR-29 论文的效应量列成一张表（mRNA 降幅 vs 成熟体降幅）。已有的数字（读全文后取得，可直接抄）： PMID 22095944 系膜细胞 miR-29a/b/c 降 28%／46%／37%（P&lt;0.05）、NRK52E 中 29a 比 29b 高 10 倍、小鼠肾中高 14 倍；PMID 21784902 只给显著性符号未给倍数，其 Smad3 结合位点在 miR-29b2 上游 22 kb；PMID 40124162 collagen 1α1 降至 33±15.2% vs BLM 组 116±35%（p&lt;0.01）。空缺的那一格是「前体降幅」——四篇都没测，这正是我的入口。 配套实验准备： 在心/肠存档样本上先测 miR-29 前体 vs 成熟体比值（区分转录 vs 降解） 周末产出物： 一页决策备忘：我的方向 2 是否仍然成立（这是 go/no-go）</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2989,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>W11 · 平台与编辑：方向 4/5 的可行性底座</t>
+          <t>W8 · 尿苷化机器：TUT4/7 与 DIS3L2 的完整通路</t>
         </is>
       </c>
     </row>
@@ -3008,7 +2997,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 我能不能用类器官 + 碱基编辑，把 TDMD 做成可定量的活体读出？ 配套计算任务： 设计 TDMD 荧光报告构建方案（内源位点敲入 vs 外源质粒，权衡写清） 配套实验准备： 盘点编辑试剂与类器官培养基；估算建系周期 周末产出物： 方向 4/5 的技术路线图一页（含建系时间线）</t>
+          <t>本周问题： 尿苷化在什么条件下把一个 miRNA 送去降解，而不是改变它的加工？ 配套计算任务： 梳理 TUT4/7 底物特异性的已知规则，判断 miR-29 是否符合 配套实验准备： 订 TUT4/TUT7 敲低试剂（siRNA/ASO）与 DIS3L2 抗体 周末产出物： 方向 2 的实验设计图（含区分转录 vs 尿苷化的关键对照）</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3009,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>W12 · 收口：竞争监视 + 写出 Specific Aims</t>
+          <t>W9 · 落点器官：肠狭窄与心脏纤维化的真实病理</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3017,7 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>本周问题： 谁正在做和我最接近的事？我的 Aims 与他们的差异能不能一句话说清？ 配套计算任务： 把 2026 年最新三篇与我的三个 Aim 逐条比对，写差异声明 配套实验准备： 确定第一个 go/no-go 实验的日期与所需试剂是否到位 周末产出物： 两页 Specific Aims 定稿，交给 3 位 PI 做「你能拥有这个问题吗」测试</t>
+          <t>本周问题： 我的两个器官模型，各自的临床终点与病理性成纤维细胞亚群是什么？ 配套计算任务： 把自己 MYBPC3 与 SAA3 两篇的表型与文献里的亚群标记对齐 配套实验准备： 设计类器官纤维化读出（胶原、硬度）的定量方案 周末产出物： 两器官对照表：共同机制 vs 器官特异机制，各写三条</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3029,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>13.3 论文记录模板 / Paper note template</t>
+          <t>W10 · 乳酰化：非组蛋白与 RNA 机器的既有先例</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3037,7 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>下面这份模板在 paper_note_template.md 与工作簿「4 笔记模板」表里都有。第 6/7/8 栏是「读者」与「审稿人」的分界线；第 9/10/11 栏（热点定位 / 空白 / 未来方向）是写申请书 Significance 与 Innovation 时直接要粘贴的内容。</t>
+          <t>本周问题： 乳酸能否直接修饰 RNA 处理酶？已有先例的证据标准是什么？ 配套计算任务： 列出所有已报道的非组蛋白乳酰化底物，看有没有 RNA 结合蛋白 配套实验准备： 与质谱平台确认乳酰化位点鉴定的可行性与样本量 周末产出物： 方向 3 的可行性判断书：做 / 降级为 Aim3 / 不做（三选一，写理由）</t>
         </is>
       </c>
     </row>
@@ -3060,171 +3049,183 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>W11 · 平台与编辑：方向 4/5 的可行性底座</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>本周问题： 我能不能用类器官 + 碱基编辑，把 TDMD 做成可定量的活体读出？ 配套计算任务： 设计 TDMD 荧光报告构建方案（内源位点敲入 vs 外源质粒，权衡写清） 配套实验准备： 盘点编辑试剂与类器官培养基；估算建系周期 周末产出物： 方向 4/5 的技术路线图一页（含建系时间线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>W12 · 收口：竞争监视 + 写出 Specific Aims</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>本周问题： 谁正在做和我最接近的事？我的 Aims 与他们的差异能不能一句话说清？ 配套计算任务： 把 2026 年最新三篇与我的三个 Aim 逐条比对，写差异声明 配套实验准备： 确定第一个 go/no-go 实验的日期与所需试剂是否到位 周末产出物： 两页 Specific Aims 定稿，交给 3 位 PI 做「你能拥有这个问题吗」测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>13.3 论文记录模板 / Paper note template</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>下面这份模板在 paper_note_template.md 与工作簿「4 笔记模板」表里都有。第 6/7/8 栏是「读者」与「审稿人」的分界线；第 9/10/11 栏（热点定位 / 空白 / 未来方向）是写申请书 Significance 与 Innovation 时直接要粘贴的内容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
           <t>论文精读记录模板 / Paper Note Template</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="1" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>复制这一整块，每篇一份。文件名/note-id 用 W&lt;周&gt;-&lt;PMID&gt;，例如 W7-21784902。</t>
         </is>
       </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr"/>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>三条硬规则 1. 没有数字的笔记不算笔记 —— 第 7 栏必须有效应量。 2. 每篇必须产出一个可执行动作 —— 第 12 栏，写进台账 A。 3. 第 6、7、8 栏是「读者」与「审稿人」的分界线 —— 三栏都空就是没读。</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>〔note-id〕W__-________  ·  读于 20__-__-__  ·  层级 T__（T0 精读/T1 速读/T2 略读）</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr"/>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>PMID ________　链接 https://pubmed.ncbi.nlm.nih.gov/________/ 标题 期刊 / 年 / 引用数 ______ / ____ / ____ 类型 ☐ 原创研究　☐ 综述　☐ 预印本　☐ 方法学 归属方向 ☐ 方向1 AMPK-ZSWIM8　☐ 方向2 TUT4/7-miR-29　☐ 方向3 乳酰化　☐ 方向4 类器官平台　☐ 方向5 编辑解剖　☐ 仅背景</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>一 · 内容（读懂它）</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr"/>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>1. 一句话结论（用我自己的话，不许抄摘要）</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr"/>
-      <c r="B279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>2. 它回答了哪个问题？</t>
+          <t>三条硬规则 1. 没有数字的笔记不算笔记 —— 第 7 栏必须有效应量。 2. 每篇必须产出一个可执行动作 —— 第 12 栏，写进台账 A。 3. 第 6、7、8 栏是「读者」与「审稿人」的分界线 —— 三栏都空就是没读。</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr"/>
-      <c r="B281" s="3" t="inlineStr"/>
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>〔note-id〕W__-________  ·  读于 20__-__-__  ·  层级 T__（T0 精读/T1 速读/T2 略读）</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>☐ 这个问题此前是开放的　☐ 这是对已知结论的补强　☐ 这是背景性综述</t>
+          <t>PMID ________　链接 https://pubmed.ncbi.nlm.nih.gov/________/ 标题 期刊 / 年 / 引用数 ______ / ____ / ____ 类型 ☐ 原创研究　☐ 综述　☐ 预印本　☐ 方法学 归属方向 ☐ 方向1 AMPK-ZSWIM8　☐ 方向2 TUT4/7-miR-29　☐ 方向3 乳酰化　☐ 方向4 类器官平台　☐ 方向5 编辑解剖　☐ 仅背景</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr"/>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>3. 关键图是哪张，为什么可信？（写图号 + 样本量 + 定量方式）</t>
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>一 · 内容（读懂它）</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
-      <c r="B284" s="3" t="inlineStr"/>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>1. 一句话结论（用我自己的话，不许抄摘要）</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>4. 方法要点（浓度／时长／细胞系／测序深度／重复数 —— 同步抄进台账 C 方法参数）</t>
-        </is>
-      </c>
+      <c r="B285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
-      <c r="B286" s="3" t="inlineStr"/>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>2. 它回答了哪个问题？</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
-      <c r="B287" s="3" t="inlineStr">
-        <is>
-          <t>5. 体系与适用边界（细胞系？小鼠？人？体外重构？结论能外推到哪一步为止）</t>
-        </is>
-      </c>
+      <c r="B287" s="3" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
-      <c r="B288" s="3" t="inlineStr"/>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>☐ 这个问题此前是开放的　☐ 这是对已知结论的补强　☐ 这是背景性综述</t>
+        </is>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>二 · 批判（读成审稿人）</t>
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>3. 关键图是哪张，为什么可信？（写图号 + 样本量 + 定量方式）</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>6. 它做了哪些对照、⚠️ 漏了哪些对照？（漏掉的对照往往就是我的切入点）</t>
-        </is>
-      </c>
+      <c r="B290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>· 做了：</t>
+          <t>4. 方法要点（浓度／时长／细胞系／测序深度／重复数 —— 同步抄进台账 C 方法参数）</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
-      <c r="B292" s="3" t="inlineStr">
-        <is>
-          <t>· 漏了：</t>
-        </is>
-      </c>
+      <c r="B292" s="3" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>7. ⚠️ 效应量（必须带数字）（倍数／百分比／n／p 值，至少一个）</t>
+          <t>5. 体系与适用边界（细胞系？小鼠？人？体外重构？结论能外推到哪一步为止）</t>
         </is>
       </c>
     </row>
@@ -3233,26 +3234,30 @@
       <c r="B294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>8. ⚠️ 有一件事我不相信（找不出来说明读得太浅，回去重读）</t>
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>二 · 批判（读成审稿人）</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
-      <c r="B296" s="3" t="inlineStr"/>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>6. 它做了哪些对照、⚠️ 漏了哪些对照？（漏掉的对照往往就是我的切入点）</t>
+        </is>
+      </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t>三 · 领域定位（这一节是写申请书时直接要用的）</t>
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>· 做了：</t>
         </is>
       </c>
     </row>
@@ -3260,43 +3265,43 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>9. 🔥 热点定位 —— 这篇处在领域的哪个位置？ ☐ 奠基（人人必引）　☐ 当前主线　☐ 上升中的子方向　☐ 已趋饱和　☐ 边缘/小众 一句话说明谁在做、为什么现在热：</t>
+          <t>· 漏了：</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
-      <c r="B299" s="3" t="inlineStr"/>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>7. ⚠️ 效应量（必须带数字）（倍数／百分比／n／p 值，至少一个）</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr"/>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>10. 🕳 它暴露/承认了哪些空白？（作者自己在 Discussion 里说「尚不清楚」的，逐条抄下来 —— 这是最省力的选题来源）</t>
-        </is>
-      </c>
+      <c r="B300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>· 空白 1：</t>
+          <t>8. ⚠️ 有一件事我不相信（找不出来说明读得太浅，回去重读）</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
-      <c r="B302" s="3" t="inlineStr">
-        <is>
-          <t>· 空白 2：</t>
-        </is>
-      </c>
+      <c r="B302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr"/>
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>· 其中哪一条我能做？为什么是我？</t>
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>三 · 领域定位（这一节是写申请书时直接要用的）</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3309,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>11. 🔭 它指向的未来方向 —— 如果这条线再往下走三年，最可能出什么？</t>
+          <t>9. 🔥 热点定位 —— 这篇处在领域的哪个位置？ ☐ 奠基（人人必引）　☐ 当前主线　☐ 上升中的子方向　☐ 已趋饱和　☐ 边缘/小众 一句话说明谁在做、为什么现在热：</t>
         </is>
       </c>
     </row>
@@ -3316,19 +3321,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>☐ 我应该跟进　☐ 我应该绕开（太拥挤）　☐ 我应该抢在前面</t>
+          <t>10. 🕳 它暴露/承认了哪些空白？（作者自己在 Discussion 里说「尚不清楚」的，逐条抄下来 —— 这是最省力的选题来源）</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>四 · 接口与行动（读完必须落地）</t>
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>· 空白 1：</t>
         </is>
       </c>
     </row>
@@ -3336,19 +3337,23 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>12. 与我课题的接口（三选一并注明具体内容） ☐ 可搬的方法 → ☐ 可用的对照值/基准数字 → ☐ ⚠️ 竞争风险 → 与我哪个 Aim 撞？我的差异声明是什么？</t>
+          <t>· 空白 2：</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
-      <c r="B309" s="3" t="inlineStr"/>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>· 其中哪一条我能做？为什么是我？</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>13. 一个可执行动作（写成「我要在 X 体系里做 Y，预期 Z」；同步进台账 A 的「我的动作」列）</t>
+          <t>11. 🔭 它指向的未来方向 —— 如果这条线再往下走三年，最可能出什么？</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3365,7 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>14. 它的哪几篇参考文献要排进我的阅读队列？（记 PMID 或首作者+年份，加进候选池） - -</t>
+          <t>☐ 我应该跟进　☐ 我应该绕开（太拥挤）　☐ 我应该抢在前面</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3377,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>五 · 归档</t>
+          <t>四 · 接口与行动（读完必须落地）</t>
         </is>
       </c>
     </row>
@@ -3380,47 +3385,31 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>关联台账 ☐ 已写入台账 A 证据　☐ 已写入台账 B 试剂　☐ 已写入台账 C 方法参数　☐ 已写入台账 D 空白/假设 本篇是否改变了我的假设？ ☐ 否　☐ 是 → 在台账 D 的「假设版本日志」里新增一行（H__ v__ → v__，并写日期与触发原因）</t>
+          <t>12. 与我课题的接口（三选一并注明具体内容） ☐ 可搬的方法 → ☐ 可用的对照值/基准数字 → ☐ ⚠️ 竞争风险 → 与我哪个 Aim 撞？我的差异声明是什么？</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>English field reference</t>
-        </is>
-      </c>
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" s="3" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Fields 6, 7 and 8 are what separate a reader from a reviewer; fields 9, 10 and 11 are what you will paste into the Significance and Innovation sections of a grant. Field 12 is how the reading plan stays connected to the bench.</t>
+          <t>13. 一个可执行动作（写成「我要在 X 体系里做 Y，预期 Z」；同步进台账 A 的「我的动作」列）</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>14 · 各方向技术与实验全清单 / Technique &amp; Experiment Inventory</t>
-        </is>
-      </c>
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" s="3" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>本节完整内容亦单独成文：techniques_by_direction.md。</t>
+          <t>14. 它的哪几篇参考文献要排进我的阅读队列？（记 PMID 或首作者+年份，加进候选池） - -</t>
         </is>
       </c>
     </row>
@@ -3432,59 +3421,55 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>各方向技术与实验全清单 / Complete Technique &amp; Experiment Inventory by Direction</t>
+          <t>五 · 归档</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="inlineStr">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>关联台账 ☐ 已写入台账 A 证据　☐ 已写入台账 B 试剂　☐ 已写入台账 C 方法参数　☐ 已写入台账 D 空白/假设 本篇是否改变了我的假设？ ☐ 否　☐ 是 → 在台账 D 的「假设版本日志」里新增一行（H__ v__ → v__，并写日期与触发原因）</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B320" s="2" t="inlineStr">
-        <is>
-          <t>Xiaodong ZOU · 2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr"/>
-      <c r="B321" s="3" t="inlineStr">
-        <is>
-          <t>读法 每张表的列固定为：技术 → 用途 → 你的现状 → 关键参数 → 必须的对照 → 常见失败模式 → 学习路径与时间 → 依据 PMID。 「你的现状」四档：✅ 已具备（CV 明确列出）· 🟡 部分（有相邻技能可迁移）· 🔴 需新学 · 🤝 需合作者（不建议自己做）。 关键参数中的 〔FILL〕 表示必须从对应 PMID 里抄到具体数值后再动手——这些格子填完就是你的 Methods 段落。</t>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>English field reference</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="inlineStr">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Fields 6, 7 and 8 are what separate a reader from a reviewer; fields 9, 10 and 11 are what you will paste into the Significance and Innovation sections of a grant. Field 12 is how the reading plan stays connected to the bench.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
-        <is>
-          <t>0 · 总技能矩阵 / Master skills matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr"/>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>●●● 关键路径 · ●● 重要 · ● 有用 · ○ 边缘 · — 不涉及</t>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>14 · 各方向技术与实验全清单 / Technique &amp; Experiment Inventory</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>1 · 方向 1：AMPK–ZSWIM8–代谢记忆</t>
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>本节完整内容亦单独成文：techniques_by_direction.md。</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3481,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>1A 激酶生化（Aim 1 的核心，也是你最大的技术缺口）</t>
+          <t>各方向技术与实验全清单 / Complete Technique &amp; Experiment Inventory by Direction</t>
         </is>
       </c>
     </row>
@@ -3508,19 +3493,15 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>1B 细胞与代谢处理</t>
+          <t>Xiaodong ZOU · 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B327" s="2" t="inlineStr">
-        <is>
-          <t>1C RNA 稳定性（Aim 2 的核心）</t>
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>读法 每张表的列固定为：技术 → 用途 → 你的现状 → 关键参数 → 必须的对照 → 常见失败模式 → 学习路径与时间 → 依据 PMID。 「你的现状」四档：✅ 已具备（CV 明确列出）· 🟡 部分（有相邻技能可迁移）· 🔴 需新学 · 🤝 需合作者（不建议自己做）。 关键参数中的 〔FILL〕 表示必须从对应 PMID 里抄到具体数值后再动手——这些格子填完就是你的 Methods 段落。</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3513,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>1D 疾病模型（Aim 3）</t>
+          <t>0 · 总技能矩阵 / Master skills matrix</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3521,7 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>类器官高糖脉冲—撤除模型（✅ 已具备）；T2D 小型猪样本（✅ 你自己的模型，但可及性待确认）；读出为 miR-29/33/375 丰度 + 靶基因恢复曲线 + 纤维化/代谢表型。对照：持续高糖组、never-exposed 组、撤除后不同时长组。</t>
+          <t>●●● 关键路径 · ●● 重要 · ● 有用 · ○ 边缘 · — 不涉及</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3533,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>2 · 方向 2：TUT4/7–miR-29 纤维化检查点</t>
+          <t>1 · 方向 1：AMPK–ZSWIM8–代谢记忆</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3545,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>3 · 方向 3：乳酸/乳酰化 × 小 RNA 稳态</t>
+          <t>1A 激酶生化（Aim 1 的核心，也是你最大的技术缺口）</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3557,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>4 · 方向 4：类器官 TDMD 报告平台</t>
+          <t>1B 细胞与代谢处理</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3569,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>5 · 方向 5：碱基编辑解剖 TDMD 功能语法</t>
+          <t>1C RNA 稳定性（Aim 2 的核心）</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3581,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>6 · 两个别人想不到、但你独有的技能迁移</t>
+          <t>1D 疾病模型（Aim 3）</t>
         </is>
       </c>
     </row>
@@ -3608,15 +3589,19 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>· 杂交瘤单抗 → 自制 phospho-ZSWIM8(S608) 抗体。 方向 1 最大的技术瓶颈是「没有好的磷酸化抗体」，而这恰好是你 CV 上明确列出的现成能力。做出来之后，这个试剂本身就是你在领域里的护城河与合作货币。免疫周期 4–6 个月，所以必须在 Q2 启动，不能等到需要时再做。 验证必须做磷酸酶处理 + S608A 突变体双阴性（PMID 15728188）。</t>
+          <t>类器官高糖脉冲—撤除模型（✅ 已具备）；T2D 小型猪样本（✅ 你自己的模型，但可及性待确认）；读出为 miR-29/33/375 丰度 + 靶基因恢复曲线 + 纤维化/代谢表型。对照：持续高糖组、never-exposed 组、撤除后不同时长组。</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>· 碱基编辑 → 内源位点点突变，而不是过表达。 审稿人对「内源位点点突变」的信任度远高于过表达质粒，而多数 RNA 生物学实验室不具备这个能力。方向 1 的 Aim 2、方向 3 的 Aim 2、方向 5 的全部，都应该建立在内源编辑之上。这一条能把你的机制结论的可信度整体提高一档。</t>
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>2 · 方向 2：TUT4/7–miR-29 纤维化检查点</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3613,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>7 · 必须找合作者的四处（不要自己做）</t>
+          <t>3 · 方向 3：乳酸/乳酰化 × 小 RNA 稳态</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3625,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>8 · 学习顺序（与 12 周阅读计划对齐）</t>
+          <t>4 · 方向 4：类器官 TDMD 报告平台</t>
         </is>
       </c>
     </row>
@@ -3652,15 +3637,19 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>English summary</t>
+          <t>5 · 方向 5：碱基编辑解剖 TDMD 功能语法</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr"/>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>A technique-by-technique inventory for all five directions, with fixed columns: technique, purpose, his current status (have / partial / must learn / needs collaborator), key parameters, mandatory controls, common failure modes, learning path and time, and the source PMID. Parameter cells marked 〔FILL〕 must be copied from the cited paper before bench work begins — filling them in produces the Methods section.</t>
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>6 · 两个别人想不到、但你独有的技能迁移</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3657,7 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>The master matrix shows the critical path is small-RNA methodology, which is learnable inside his current lab at zero cost, followed by half-life measurement and kinase biochemistry. Three controls are called out as non-negotiable because omitting them invalidates the result rather than merely weakening it: a canonical AMPK substrate on the same gel as any in-vitro kinase assay; pri/pre-versus-mature measurement in Direction 2, without which the result is fully explained by the established TGF-β/Smad3 transcriptional mechanism; and a pH-matched plus non-metabolic-acidification control in Direction 3, without which any lactate effect is confounded.</t>
+          <t>· 杂交瘤单抗 → 自制 phospho-ZSWIM8(S608) 抗体。 方向 1 最大的技术瓶颈是「没有好的磷酸化抗体」，而这恰好是你 CV 上明确列出的现成能力。做出来之后，这个试剂本身就是你在领域里的护城河与合作货币。免疫周期 4–6 个月，所以必须在 Q2 启动，不能等到需要时再做。 验证必须做磷酸酶处理 + S608A 突变体双阴性（PMID 15728188）。</t>
         </is>
       </c>
     </row>
@@ -3676,21 +3665,81 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" s="3" t="inlineStr">
         <is>
+          <t>· 碱基编辑 → 内源位点点突变，而不是过表达。 审稿人对「内源位点点突变」的信任度远高于过表达质粒，而多数 RNA 生物学实验室不具备这个能力。方向 1 的 Aim 2、方向 3 的 Aim 2、方向 5 的全部，都应该建立在内源编辑之上。这一条能把你的机制结论的可信度整体提高一档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>7 · 必须找合作者的四处（不要自己做）</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>8 · 学习顺序（与 12 周阅读计划对齐）</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>English summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>A technique-by-technique inventory for all five directions, with fixed columns: technique, purpose, his current status (have / partial / must learn / needs collaborator), key parameters, mandatory controls, common failure modes, learning path and time, and the source PMID. Parameter cells marked 〔FILL〕 must be copied from the cited paper before bench work begins — filling them in produces the Methods section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>The master matrix shows the critical path is small-RNA methodology, which is learnable inside his current lab at zero cost, followed by half-life measurement and kinase biochemistry. Three controls are called out as non-negotiable because omitting them invalidates the result rather than merely weakening it: a canonical AMPK substrate on the same gel as any in-vitro kinase assay; pri/pre-versus-mature measurement in Direction 2, without which the result is fully explained by the established TGF-β/Smad3 transcriptional mechanism; and a pH-matched plus non-metabolic-acidification control in Direction 3, without which any lactate effect is confounded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
           <t>Two skill transfers from his own CV are singled out as unusually high-leverage: hybridoma capability lets him raise his own phospho-ZSWIM8(S608) antibody against the field's main reagent bottleneck — and because the immunisation cycle runs 4–6 months, this is the one item that must start in Q2 rather than when it is needed; and base editing lets him install point mutants at endogenous loci instead of relying on overexpression, which raises the credibility of every mechanistic claim and is something most RNA-biology labs cannot do.</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr"/>
-      <c r="B343" s="3" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" s="3" t="inlineStr">
         <is>
           <t>Four gaps should be filled by collaborators rather than learned: phospho/lactyl mass spectrometry (mandatory, and the negotiation should start in Q1–Q2), structural interpretation of site accessibility, human fibrosis specimens, and deep computational half-life modelling.</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr"/>
-      <c r="B344" s="3" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" s="3" t="inlineStr">
         <is>
           <t>*报告依据：Zou Xiaodong CV_20251027_Update.pdf（17 篇发表、9 项基金）+ 本项目此前核对的 Google Scholar 记录。所有 PMID 经 Europe PMC 核实。引用数为抓取当日值，会随时间变化。*</t>
         </is>
@@ -3719,7 +3768,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>阅读顺序与时间安排 / Reading order and time budget</t>
+          <t>阅读顺序与时间安排（粗排，已被 §13 取代）/ Reading order and time budget</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4499,131 +4548,63 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>缺什么</t>
+          <t>新缺口</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>为什么要</t>
+          <t>影响哪一节</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Lai lab 对你 side project 的授权边界——问题归属、数据能否带走</t>
+          <t>miR-29 三个成员丰度差 5–14 倍（PMID 22095944 Fig.1F），文献普遍用合并读出</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>这是第 8 节整张表的单点故障，也决定「独立性」叙事能否成立</t>
+          <t>§12 方向 2 Aim 1 的样本量与内参必须按最低丰度成员定</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>你的签证/身份状态（H-1B？J-1？绿卡进程？）</t>
+          <t>ZSWIM8 的线虫同源物 EBAX-1 有非 TDMD 功能（驱动 linker cell 非凋亡死亡，PMID 41542532）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>直接决定美国路径（K99 已基本关门、F32 需公民/绿卡）是否还有意义，以及亚洲路径的时间窗</t>
+          <t>§12 方向 1 Aim 3：KO 表型不能直接归因于 TDMD，必须补底物层证据</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>手上真实的未发表数据清单</t>
+          <t>代谢记忆那条线的证据基础主要来自视网膜/内皮细胞，PMID 41465114 全文未涉及任何 miRNA 稳态蛋白</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>你此前明确说 ZSWIM8 方向无未发表数据；若其他方向有，能大幅改变 Q1–Q2 的排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>存档样本的实际可及性——MYBPC3 心脏与 SAA3 肠组织现在还在不在、在谁手里</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>方向 2「零成本起步」完全依赖这一点</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>教学/带学生记录</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>faculty 申请必需，CV 目前只有辅导员与学生工作，没有科研 mentoring 记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>年龄/毕业年限的准确数字</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>海外优青等有年龄上限与博士学位年限要求，需精确到月</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>可用的推荐人名单与他们的意愿</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Q4 需要 3 位通讯级推荐人</t>
+          <t>§12 方向 1 的疾病叙事仍缺器官特异（肾小管/胰岛）的复糖-撤糖对照文献</t>
         </is>
       </c>
     </row>
@@ -4633,6 +4614,185 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>缺什么</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>为什么要</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Lai lab 对你 side project 的授权边界——问题归属、数据能否带走</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>这是第 8 节整张表的单点故障，也决定「独立性」叙事能否成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>你的签证/身份状态（H-1B？J-1？绿卡进程？）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>直接决定美国路径（K99 已基本关门、F32 需公民/绿卡）是否还有意义，以及亚洲路径的时间窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>手上真实的未发表数据清单</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>你此前明确说 ZSWIM8 方向无未发表数据；若其他方向有，能大幅改变 Q1–Q2 的排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>存档样本的实际可及性——MYBPC3 心脏与 SAA3 肠组织现在还在不在、在谁手里</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>方向 2「零成本起步」完全依赖这一点</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>那 3 篇无开放全文的原文（20201077 硬化症 miR-29、20421885 代谢记忆综述、42622514 狭窄型克罗恩蛋白质组）——MSKCC 订阅能否取到</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>取到后可把替代文献换回原文并恢复层级；替代只是让计划不断档</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>教学/带学生记录</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>faculty 申请必需，CV 目前只有辅导员与学生工作，没有科研 mentoring 记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>年龄/毕业年限的准确数字</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>海外优青等有年龄上限与博士学位年限要求，需精确到月</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>可用的推荐人名单与他们的意愿</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Q4 需要 3 位通讯级推荐人</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4725,17 +4885,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
@@ -4816,12 +4976,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2b</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>AGO2 亦可保护 miRNA 免于 TDMD —— 降解/保护是可调平衡</t>
+          <t>机器的靶标判别有定量尺度：ZSWIM8 对「trigger 配对」复合体的共沉淀偏好达 up to 70 倍；加入 trigger 侧翼序列（+85 nt）后共沉淀效率再提升 100 倍——无侧翼需 300 nM ZSWIM8 才达 15% pulldown，有侧翼仅需 3 nM</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4831,19 +4991,19 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>PMID 33853897</t>
+          <t>PMID 41542392（Farnung &amp; Slobodyanyuk，通讯 Schulman/Bartel）Fig 1e/1f。对我的意义：这给了 Aim 2 体外重构的动态范围（3 nM–300 nM 两个数量级），磷酸化若改变判别效率，应能在这个窗口内读出</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>AMPK 底物基序为 −3/−4 碱性 + +4 疏水</t>
+          <t>AGO2 亦可保护 miRNA 免于 TDMD —— 降解/保护是可调平衡</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4853,73 +5013,117 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>PMID 7698321（原始生化）；PMID 25683918（基序亲和 + 质谱发现流程）</t>
+          <t>PMID 33853897</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>ZSWIM8-S608/S609 落在该基序内、且处于无序区（易被激酶接近）</t>
+          <t>AMPK 底物基序为 −3/−4 碱性 + +4 疏水</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>[本项目计算]</t>
+          <t>[已发表]</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>自建透明 PSSM：S609 98.3 百分位 / S608 96.4 / S1202 82.7。分值本身不构成证据</t>
+          <t>PMID 7698321（原始生化）；PMID 25683918（基序亲和 + 质谱发现流程）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>代谢记忆存在且具表观遗传基础</t>
+          <t>ZSWIM8-S608/S609 落在该基序内、且处于无序区（易被激酶接近）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>[已发表]</t>
+          <t>[本项目计算]</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>PMID 25481708；PMID 42321894（2026 综述，miRNA 与高血糖代谢记忆）</t>
+          <t>自建透明 PSSM：S609 98.3 百分位 / S608 96.4 / S1202 82.7。分值本身不构成证据</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>代谢记忆存在且具表观遗传基础</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[已发表]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>PMID 25481708；PMID 42321894（2026 综述，miRNA 与高血糖代谢记忆）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>上游信号如何调控 miRNA 降解机器 —— 几乎空白</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>[待测]</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>AMPK 已知底物分类中几乎没有 RNA 结合蛋白（PMID 26616193）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ ZSWIM8 的功能不止 TDMD：其线虫同源物 EBAX-1 驱动 linker cell 的非凋亡性程序性死亡（野生型 97% 的 linker cell 在 L4→成虫后 24 h 已降解，n=241；ebax-1 突变体 44% 存活，linker-cell 特异性回复后降至 7%）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>[已发表]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>PMID 41542532。对 Aim 3 的直接约束：ZSWIM8-KO 在代谢记忆模型里出现表型，不能直接归因于 TDMD——必须同时给出底物层证据（该 miRNA 半衰期改变 + 触发靶标依赖性），否则归因会被审稿人打回</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5025,17 +5229,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
@@ -5087,7 +5291,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>肝 PMID 20890893；肾 21784902；肺 20971881；皮肤/SSc 20201077</t>
+          <t>肝 PMID 20890893；肾 21784902；肺 20971881。（原引的皮肤/SSc PMID 20201077 无开放全文，阅读计划中已换为 PMID 40124162 —— 见 §13 替代说明）</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5325,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>miR-29 下降由 TGF-β/Smad3 在转录层驱动</t>
+          <t>miR-29 下降由 TGF-β/Smad3 在转录层驱动 —— 且已被定量到位</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -5131,7 +5335,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>PMID 21784902、22095944 —— 这是我的降解假设最强的替代解释</t>
+          <t>PMID 22095944：系膜细胞中 TGF-β1 处理后 miR-29a/b/c 分别下降 28%／46%／37%（P&lt;0.05）；Fig.4A–C 用 collagen I、IVa1、IVa3 三个 3′UTR 荧光素酶报告基因证明 miR-29 直接压制，Fig.4D 用结合位点突变体证明序列特异性。PMID 21784902：Smad3 结合位点定位在 miR-29b2 启动子上游 22 kb（Fig.3A），并有 Smad3-KO 小鼠与 MEF 的 Smad3 vs Smad2 分离对照。这是我的降解假设最强的替代解释，且它的证据链比我原先估计的更完整</t>
         </is>
       </c>
     </row>
@@ -5176,6 +5380,28 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>文献普遍只测成熟体丰度，未测 3′ 末端</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ miR-29 三个成员丰度差一个量级：NRK52E 中 miR-29a 比 miR-29b 高 10 倍、比 miR-29c 高 5 倍；小鼠肾脏中 miR-29a 比 miR-29b 高 14 倍</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>[已发表]</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>PMID 22095944 Fig.1F。对 Aim 1 的直接后果：三个成员必须分开定量、不能用「miR-29」一个合并读出；且低丰度成员（29b/29c）的降解信号更容易被测量噪声吞掉——样本量与内参选择要按最低丰度的那个成员来定</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5335,258 +5561,6 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>检索 632 篇候选池中未见报道 —— 这是真空白</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>五方向决策表 / Decision matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>新颖度</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>启动成本</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>首篇时间</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>可持续性</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>建议定位</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1 AMPK–ZSWIM8–代谢记忆</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>中-高</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>12–18 月</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>主线（冲顶刊与大基金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2 TUT4/7–miR-29 纤维化</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>中-高</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>接近零</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>9–12 月</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>主线（保产出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3 乳酸/乳酰化 × 小 RNA</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>最高（真空白）</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>中（需质谱合作）</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>18–30 月</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>3.3→上升</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>方向 1 的 Aim 3 / 种子基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4 类器官 TDMD 报告平台</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>低-中</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>12–18 月</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>资源牌、合作与平台经费</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5 碱基编辑解剖 TDMD</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>低（你已有技能）</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>随 1/3</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>机制手术刀，不独立立项</t>
         </is>
       </c>
     </row>
@@ -5788,6 +5762,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>五方向决策表 / Decision matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>新颖度</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>难度</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>启动成本</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>首篇时间</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>可持续性</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>建议定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1 AMPK–ZSWIM8–代谢记忆</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>中-高</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>12–18 月</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>主线（冲顶刊与大基金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2 TUT4/7–miR-29 纤维化</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>中-高</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>接近零</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>9–12 月</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>主线（保产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3 乳酸/乳酰化 × 小 RNA</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>最高（真空白）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>中（需质谱合作）</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>18–30 月</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>3.3→上升</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>方向 1 的 Aim 3 / 种子基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4 类器官 TDMD 报告平台</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>低-中</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>12–18 月</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>资源牌、合作与平台经费</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>5 碱基编辑解剖 TDMD</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>低（你已有技能）</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>随 1/3</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>机制手术刀，不独立立项</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6227,7 +6453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6544,289 +6770,6 @@
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>三种 miRNA 降解路线的判别性实验分别是什么</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="49" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="53" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>W2 · 机器的边界、保护面与结构约束</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>层级</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>PMID</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>期刊</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>为什么读</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>必须记下什么</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>[34819352](https://pubmed.ncbi.nlm.nih.gov/34819352/)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Genes &amp; development</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Widespread microRNA degradation elements in target mRNAs can assist the encoded proteins</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>广泛存在的 miRNA 降解元件——说明 TDMD 是普遍机制而非特例</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>有多少个内源触发转录本；他们如何从头预测并验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>[33853897](https://pubmed.ncbi.nlm.nih.gov/33853897/)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>RNA (New York, N.Y.)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Ago2 protects Drosophila siRNAs and microRNAs from target-directed degradation, even in the absence of 2'-O-methylation</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>反面：AGO2 如何保护 miRNA 免于 TDMD——降解与保护是一对平衡</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>保护的分子基础；这是否给「信号调控」提供了另一个作用点</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>[37532519](https://pubmed.ncbi.nlm.nih.gov/37532519/)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Genome research</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>ZSWIM8 destabilizes many murine microRNAs and is required for proper embryonic growth and development</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>ZSWIM8 敲除的全局后果，给出体内可测的表型谱</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>被稳定的 miRNA 名单里有没有代谢相关的（miR-29/33/375）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>[41851464](https://pubmed.ncbi.nlm.nih.gov/41851464/)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>The E3 ubiquitin ligase mechanism specifying targeted microRNA degradation</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>ZSWIM8–AGO2–靶标复合体冷冻电镜结构：位点可及性的直接证据</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>S608/S609 所在的无序区在结构里是否被解析；若未解析说明它柔性暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>[39702526](https://pubmed.ncbi.nlm.nih.gov/39702526/)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Nature reviews. Molecular cell bio</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>The biogenesis and regulation of animal microRNAs</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>2025 年 Nat Rev 综述：miRNA 生成与调控全景</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>调控层级图；我要插入的「信号→降解」这一层在图上有没有</t>
         </is>
       </c>
     </row>
@@ -6851,13 +6794,13 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>W3 · 把「半衰期」变成可测量的数字</t>
+          <t>W2 · 机器的边界、保护面与结构约束</t>
         </is>
       </c>
     </row>
@@ -6911,37 +6854,37 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>[31519739](https://pubmed.ncbi.nlm.nih.gov/31519739/)</t>
+          <t>[34819352](https://pubmed.ncbi.nlm.nih.gov/34819352/)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Genome research</t>
+          <t>Genes &amp; development</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Global analyses of the dynamics of mammalian microRNA metabolism</t>
+          <t>Widespread microRNA degradation elements in target mRNAs can assist the encoded proteins</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>哺乳动物 miRNA 代谢动力学的全局测定——半衰期数值的基准来源</t>
+          <t>广泛存在的 miRNA 降解元件——说明 TDMD 是普遍机制而非特例</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>典型 miRNA 半衰期范围；他们用的标记方式与归一化；哪些 miRNA 是短命的</t>
+          <t>有多少个内源触发转录本；他们如何从头预测并验证</t>
         </is>
       </c>
     </row>
@@ -6953,121 +6896,121 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>[21447562](https://pubmed.ncbi.nlm.nih.gov/21447562/)</t>
+          <t>[33853897](https://pubmed.ncbi.nlm.nih.gov/33853897/)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Nucleic acids research</t>
+          <t>RNA (New York, N.Y.)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Analysis of microRNA turnover in mammalian cells following Dicer1 ablation</t>
+          <t>Ago2 protects Drosophila siRNAs and microRNAs from target-directed degradation, even in the absence of 2'-O-methylation</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>经典：用 Dicer1 敲除法测 miRNA 周转</t>
+          <t>反面：AGO2 如何保护 miRNA 免于 TDMD——降解与保护是一对平衡</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>这种方法的偏倚在哪；为什么需要多种正交方法</t>
+          <t>保护的分子基础；这是否给「信号调控」提供了另一个作用点</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>[28945705](https://pubmed.ncbi.nlm.nih.gov/28945705/)</t>
+          <t>[37532519](https://pubmed.ncbi.nlm.nih.gov/37532519/)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Nature methods</t>
+          <t>Genome research</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Thiol-linked alkylation of RNA to assess expression dynamics</t>
+          <t>ZSWIM8 destabilizes many murine microRNAs and is required for proper embryonic growth and development</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>SLAM-seq：代谢标记测 RNA 动态的方法学标杆</t>
+          <t>ZSWIM8 敲除的全局后果，给出体内可测的表型谱</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>标记时长、转化率、测序深度、如何区分新合成与既有 RNA</t>
+          <t>被稳定的 miRNA 名单里有没有代谢相关的（miR-29/33/375）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>[24582499](https://pubmed.ncbi.nlm.nih.gov/24582499/)</t>
+          <t>[41851464](https://pubmed.ncbi.nlm.nih.gov/41851464/)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Molecular cell</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>TAIL-seq: genome-wide determination of poly(A) tail length and 3' end modifications</t>
+          <t>The E3 ubiquitin ligase mechanism specifying targeted microRNA degradation</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>TAIL-seq：3′ 末端与尾巴长度的全基因组测定——方向 2 的核心方法</t>
+          <t>ZSWIM8–AGO2–靶标复合体冷冻电镜结构：位点可及性的直接证据</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>建库关键步骤；能分辨几个核苷酸的尾巴；对小 RNA 需要怎么改</t>
+          <t>S608/S609 所在的无序区在结构里是否被解析；若未解析说明它柔性暴露</t>
         </is>
       </c>
     </row>
@@ -7079,37 +7022,37 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>[41608885](https://pubmed.ncbi.nlm.nih.gov/41608885/)</t>
+          <t>[39702526](https://pubmed.ncbi.nlm.nih.gov/39702526/)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Wiley interdisciplinary reviews. R</t>
+          <t>Nature reviews. Molecular cell bio</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>MiRNA Stability and Degradation: Dynamic Regulators of Cellular Regulatory Networks</t>
+          <t>The biogenesis and regulation of animal microRNAs</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026 年 miRNA 稳定性与降解综述，补齐最新图景</t>
+          <t>2025 年 Nat Rev 综述：miRNA 生成与调控全景</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>最近两年新出现的降解通路有哪些</t>
+          <t>调控层级图；我要插入的「信号→降解」这一层在图上有没有</t>
         </is>
       </c>
     </row>
@@ -7133,14 +7076,14 @@
     <col width="49" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>W4 · AMPK 底物识别语法——决定我的位点预测可不可信</t>
+          <t>W3 · 把「半衰期」变成可测量的数字</t>
         </is>
       </c>
     </row>
@@ -7194,37 +7137,37 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>[7698321](https://pubmed.ncbi.nlm.nih.gov/7698321/)</t>
+          <t>[31519739](https://pubmed.ncbi.nlm.nih.gov/31519739/)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>FEBS letters</t>
+          <t>Genome research</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Similar substrate recognition motifs for mammalian AMP-activated protein kinase, higher plant HMG-CoA reductase kinase-A, yeast SNF1, and mammalian calmodulin-dependent protein kinase I</t>
+          <t>Global analyses of the dynamics of mammalian microRNA metabolism</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>AMPK 底物识别基序的原始生化确立——我的 PSSM 的合法性根源</t>
+          <t>哺乳动物 miRNA 代谢动力学的全局测定——半衰期数值的基准来源</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>基序的位置权重（−3/−4 碱性、+4 疏水）；他们用什么肽库确定的</t>
+          <t>典型 miRNA 半衰期范围；他们用的标记方式与归一化；哪些 miRNA 是短命的</t>
         </is>
       </c>
     </row>
@@ -7236,163 +7179,163 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>[25683918](https://pubmed.ncbi.nlm.nih.gov/25683918/)</t>
+          <t>[21447562](https://pubmed.ncbi.nlm.nih.gov/21447562/)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Cellular signalling</t>
+          <t>Nucleic acids research</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Motif affinity and mass spectrometry proteomic approach for the discovery of cellular AMPK targets: identification of mitochondrial fission factor as a new AMPK substrate</t>
+          <t>Analysis of microRNA turnover in mammalian cells following Dicer1 ablation</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>基序亲和 + 质谱发现 AMPK 底物的完整方法论</t>
+          <t>经典：用 Dicer1 敲除法测 miRNA 周转</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>从预测到验证的证据链有几步；哪一步是不可省的</t>
+          <t>这种方法的偏倚在哪；为什么需要多种正交方法</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>[11902845](https://pubmed.ncbi.nlm.nih.gov/11902845/)</t>
+          <t>[28945705](https://pubmed.ncbi.nlm.nih.gov/28945705/)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Journal of molecular biology</t>
+          <t>Nature methods</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Protein kinase substrate recognition studied using the recombinant catalytic domain of AMP-activated protein kinase and a model substrate</t>
+          <t>Thiol-linked alkylation of RNA to assess expression dynamics</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>用重组催化域研究激酶底物特异性的方法</t>
+          <t>SLAM-seq：代谢标记测 RNA 动态的方法学标杆</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>体外激酶反应的必备对照；如何排除非特异磷酸化</t>
+          <t>标记时长、转化率、测序深度、如何区分新合成与既有 RNA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>[26616193](https://pubmed.ncbi.nlm.nih.gov/26616193/)</t>
+          <t>[24582499](https://pubmed.ncbi.nlm.nih.gov/24582499/)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Trends in cell biology</t>
+          <t>Molecular cell</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>393</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>AMPK: An Energy-Sensing Pathway with Multiple Inputs and Outputs</t>
+          <t>TAIL-seq: genome-wide determination of poly(A) tail length and 3' end modifications</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>AMPK 通路的输入-输出全景综述</t>
+          <t>TAIL-seq：3′ 末端与尾巴长度的全基因组测定——方向 2 的核心方法</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>AMPK 已知底物的功能分类；有没有 RNA 结合蛋白类底物（预期几乎没有——这就是我的空白）</t>
+          <t>建库关键步骤；能分辨几个核苷酸的尾巴；对小 RNA 需要怎么改</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>[32696389](https://pubmed.ncbi.nlm.nih.gov/32696389/)</t>
+          <t>[41608885](https://pubmed.ncbi.nlm.nih.gov/41608885/)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Methods in molecular biology (Clif</t>
+          <t>Wiley interdisciplinary reviews. R</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Detection of Multisite Phosphorylation of Intrinsically Disordered Proteins Using Phos-tag SDS-PAGE</t>
+          <t>MiRNA Stability and Degradation: Dynamic Regulators of Cellular Regulatory Networks</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Phos-tag 检测无序蛋白多位点磷酸化——S608 正好在无序区</t>
+          <t>2026 年 miRNA 稳定性与降解综述，补齐最新图景</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Phos-tag 胶的条件；如何定量磷酸化化学计量比</t>
+          <t>最近两年新出现的降解通路有哪些</t>
         </is>
       </c>
     </row>
@@ -7416,14 +7359,14 @@
     <col width="49" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>W5 · 信号 × miRNA：既有证据与反向因果的威胁</t>
+          <t>W4 · AMPK 底物识别语法——决定我的位点预测可不可信</t>
         </is>
       </c>
     </row>
@@ -7477,205 +7420,205 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>[37653034](https://pubmed.ncbi.nlm.nih.gov/37653034/)</t>
+          <t>[7698321](https://pubmed.ncbi.nlm.nih.gov/7698321/)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Experimental &amp; molecular medicine</t>
+          <t>FEBS letters</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>MicroRNA regulation of AMPK in nonalcoholic fatty liver disease</t>
+          <t>Similar substrate recognition motifs for mammalian AMP-activated protein kinase, higher plant HMG-CoA reductase kinase-A, yeast SNF1, and mammalian calmodulin-dependent protein kinase I</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>AMPK 与 miRNA 互作的专门综述——我的直接上游文献</t>
+          <t>AMPK 底物识别基序的原始生化确立——我的 PSSM 的合法性根源</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>综述覆盖的是哪个因果方向；有没有提到 miRNA 降解机器</t>
+          <t>基序的位置权重（−3/−4 碱性、+4 疏水）；他们用什么肽库确定的</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>[20227367](https://pubmed.ncbi.nlm.nih.gov/20227367/)</t>
+          <t>[25683918](https://pubmed.ncbi.nlm.nih.gov/25683918/)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Molecular cell</t>
+          <t>Cellular signalling</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>MicroRNA-451 regulates LKB1/AMPK signaling and allows adaptation to metabolic stress in glioma cells</t>
+          <t>Motif affinity and mass spectrometry proteomic approach for the discovery of cellular AMPK targets: identification of mitochondrial fission factor as a new AMPK substrate</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>miR-451 调控 LKB1/AMPK——反向因果的代表作，必须正面处理</t>
+          <t>基序亲和 + 质谱发现 AMPK 底物的完整方法论</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>它的证据链有多强；审稿人会不会用它质疑我的方向</t>
+          <t>从预测到验证的证据链有几步；哪一步是不可省的</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>[31186373](https://pubmed.ncbi.nlm.nih.gov/31186373/)</t>
+          <t>[11902845](https://pubmed.ncbi.nlm.nih.gov/11902845/)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Science signaling</t>
+          <t>Journal of molecular biology</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>AMPK directly activates mTORC2 to promote cell survival during acute energetic stress</t>
+          <t>Protein kinase substrate recognition studied using the recombinant catalytic domain of AMP-activated protein kinase and a model substrate</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>AMPK 直接激活 mTORC2：AMPK 作为直接激酶的可信先例</t>
+          <t>用重组催化域研究激酶底物特异性的方法</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>他们如何证明「直接」；我要照搬哪几个对照</t>
+          <t>体外激酶反应的必备对照；如何排除非特异磷酸化</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>[15728188](https://pubmed.ncbi.nlm.nih.gov/15728188/)</t>
+          <t>[26616193](https://pubmed.ncbi.nlm.nih.gov/26616193/)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>The Journal of biological chemistr</t>
+          <t>Trends in cell biology</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>A phosphorylation state-specific antibody recognizes Hsp27, a novel substrate of protein kinase D</t>
+          <t>AMPK: An Energy-Sensing Pathway with Multiple Inputs and Outputs</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>磷酸化状态特异抗体的制备与验证范式</t>
+          <t>AMPK 通路的输入-输出全景综述</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>抗体验证的最低标准（磷酸酶处理、位点突变体）</t>
+          <t>AMPK 已知底物的功能分类；有没有 RNA 结合蛋白类底物（预期几乎没有——这就是我的空白）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>[27667718](https://pubmed.ncbi.nlm.nih.gov/27667718/)</t>
+          <t>[32696389](https://pubmed.ncbi.nlm.nih.gov/32696389/)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>Methods in molecular biology (Clif</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Global Phosphoproteomic Analysis Reveals the Involvement of Phosphorylation in Aflatoxins Biosynthesis in the Pathogenic Fungus Aspergillus flavus</t>
+          <t>Detection of Multisite Phosphorylation of Intrinsically Disordered Proteins Using Phos-tag SDS-PAGE</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>全局磷酸化蛋白组学的读法</t>
+          <t>Phos-tag 检测无序蛋白多位点磷酸化——S608 正好在无序区</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>位点定位概率阈值；FDR 怎么看</t>
+          <t>Phos-tag 胶的条件；如何定量磷酸化化学计量比</t>
         </is>
       </c>
     </row>
@@ -7696,17 +7639,17 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>W6 · 代谢记忆：疾病叙事与已有机制解释</t>
+          <t>W5 · 信号 × miRNA：既有证据与反向因果的威胁</t>
         </is>
       </c>
     </row>
@@ -7760,205 +7703,205 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>[25481708](https://pubmed.ncbi.nlm.nih.gov/25481708/)</t>
+          <t>[37653034](https://pubmed.ncbi.nlm.nih.gov/37653034/)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Diabetologia</t>
+          <t>Experimental &amp; molecular medicine</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Epigenetic mechanisms in diabetic complications and metabolic memory</t>
+          <t>MicroRNA regulation of AMPK in nonalcoholic fatty liver disease</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>代谢记忆的表观遗传机制经典综述——疾病概念的来源</t>
+          <t>AMPK 与 miRNA 互作的专门综述——我的直接上游文献</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>既有解释分几类；哪一类最被接受；RNA 稳定性有没有被提及</t>
+          <t>综述覆盖的是哪个因果方向；有没有提到 miRNA 降解机器</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>[42321894](https://pubmed.ncbi.nlm.nih.gov/42321894/)</t>
+          <t>[20227367](https://pubmed.ncbi.nlm.nih.gov/20227367/)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Diabetology &amp; metabolic syndrome</t>
+          <t>Molecular cell</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>MiRNAs in hyperglycemia-induced metabolic memory: established mechanisms and emerging nuclear activation concepts</t>
+          <t>MicroRNA-451 regulates LKB1/AMPK signaling and allows adaptation to metabolic stress in glioma cells</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026 年综述：miRNA 在高血糖诱导的代谢记忆中的作用——离我最近的已发表论述</t>
+          <t>miR-451 调控 LKB1/AMPK——反向因果的代表作，必须正面处理</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>它讲的是 miRNA 表达变化还是降解变化；我的角度是否仍然空白</t>
+          <t>它的证据链有多强；审稿人会不会用它质疑我的方向</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>[28452927](https://pubmed.ncbi.nlm.nih.gov/28452927/)</t>
+          <t>[31186373](https://pubmed.ncbi.nlm.nih.gov/31186373/)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Nutrients</t>
+          <t>Science signaling</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>The "Metabolic Memory" Theory and the Early Treatment of Hyperglycemia in Prevention of Diabetic Complications</t>
+          <t>AMPK directly activates mTORC2 to promote cell survival during acute energetic stress</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>代谢记忆理论与早期干预的临床语境</t>
+          <t>AMPK 直接激活 mTORC2：AMPK 作为直接激酶的可信先例</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>临床证据的强度与队列（用于写 Significance 的数字）</t>
+          <t>他们如何证明「直接」；我要照搬哪几个对照</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>[20421885](https://pubmed.ncbi.nlm.nih.gov/20421885/)</t>
+          <t>[15728188](https://pubmed.ncbi.nlm.nih.gov/15728188/)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Nature reviews. Nephrology</t>
+          <t>The Journal of biological chemistr</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms</t>
+          <t>A phosphorylation state-specific antibody recognizes Hsp27, a novel substrate of protein kinase D</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>糖尿病肾病中的代谢记忆与表观遗传</t>
+          <t>磷酸化状态特异抗体的制备与验证范式</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>器官特异性证据</t>
+          <t>抗体验证的最低标准（磷酸酶处理、位点突变体）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>[15538371](https://pubmed.ncbi.nlm.nih.gov/15538371/)</t>
+          <t>[27667718](https://pubmed.ncbi.nlm.nih.gov/27667718/)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Scientific reports</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>A pancreatic islet-specific microRNA regulates insulin secretion</t>
+          <t>Global Phosphoproteomic Analysis Reveals the Involvement of Phosphorylation in Aflatoxins Biosynthesis in the Pathogenic Fungus Aspergillus flavus</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>miR-375 调控胰岛素分泌——候选 miRNA 的功能依据</t>
+          <t>全局磷酸化蛋白组学的读法</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>miR-375 的功能强度；敲低/过表达的表型</t>
+          <t>位点定位概率阈值；FDR 怎么看</t>
         </is>
       </c>
     </row>
@@ -7968,6 +7911,289 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>W6 · 代谢记忆：疾病叙事与已有机制解释</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>为什么读</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>必须记下什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>[25481708](https://pubmed.ncbi.nlm.nih.gov/25481708/)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Diabetologia</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Epigenetic mechanisms in diabetic complications and metabolic memory</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>代谢记忆的表观遗传机制经典综述——疾病概念的来源</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>既有解释分几类；哪一类最被接受；RNA 稳定性有没有被提及</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>[42321894](https://pubmed.ncbi.nlm.nih.gov/42321894/)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Diabetology &amp; metabolic syndrome</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MiRNAs in hyperglycemia-induced metabolic memory: established mechanisms and emerging nuclear activation concepts</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2026 年综述：miRNA 在高血糖诱导的代谢记忆中的作用——离我最近的已发表论述</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>它讲的是 miRNA 表达变化还是降解变化；我的角度是否仍然空白</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>[28452927](https://pubmed.ncbi.nlm.nih.gov/28452927/)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Nutrients</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>The "Metabolic Memory" Theory and the Early Treatment of Hyperglycemia in Prevention of Diabetic Complications</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>代谢记忆理论与早期干预的临床语境</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>临床证据的强度与队列（用于写 Significance 的数字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>[41465114](https://pubmed.ncbi.nlm.nih.gov/41465114/)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Genes</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>From Metabolic to Epigenetic Memory: The Impact of Hyperglycemia-Induced Epigenetic Signature</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>【替代】原 PMID 20421885（Nat Rev Nephrol 2010）无开放全文，换成同命题 2025 年版</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>①它把记忆机制分成 AGE 形成／ROS-线粒体损伤／表观修饰／持续表达改变四臂（Fig.1）——但 Fig.1/Fig.3 是 BioRender 示意图，不是数据图，只能当框架引用；②可直接用的硬数字只有 GBD 的 57.6%／43.2%（空腹血糖受损与高血压对 CKD 发病率的贡献）与「高糖 14 天 + 复糖 7 天后 fibronectin mRNA 持续过表达数周」；③全文未涉及 AGO2／TUT4-7／ZSWIM8 任何 miRNA 稳态机制，我的角度在这篇里仍然是空白</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>[15538371](https://pubmed.ncbi.nlm.nih.gov/15538371/)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>A pancreatic islet-specific microRNA regulates insulin secretion</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>miR-375 调控胰岛素分泌——候选 miRNA 的功能依据</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>miR-375 的功能强度；敲低/过表达的表型</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7983,7 +8209,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8206,42 +8432,42 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>[20201077](https://pubmed.ncbi.nlm.nih.gov/20201077/)</t>
+          <t>[40124162](https://pubmed.ncbi.nlm.nih.gov/40124162/)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Arthritis and rheumatism</t>
+          <t>Molecular therapy. Nucleic acids</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis</t>
+          <t>Ratio of miRNA-29 to miRNA-199 expression coordinates mesenchymal stem cell repair of bleomycin-induced pulmonary injury</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>系统性硬化中 miR-29 作为胶原关键调控者</t>
+          <t>【替代】原 PMID 20201077（Arthritis Rheum 2010，皮肤/SSc）无开放全文。另一候选 PMID 40021656 正好是硬化症皮肤，但其机制是 TGF-β1/Smad3、miR-29 零提及，故选保留 miR-29 机制主体的这篇；代价是组织从皮肤换成肺，与 20971881 重叠</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>人源样本证据</t>
+          <t>①miR-29:miR-199 比值是本文核心读出——这是一个我可以直接测的协调变量，比单测 miR-29 更抗噪；②治疗窗口：ASC 在 day 12（纤维化已建立后）给药仍有效，collagen 1α1 降至 33±15.2%（vs BLM 组 116±35%，p&lt;0.01）；③因果验证只用双转染（29KI/199KO），没有单独敲低/过表达对照，无法拆开两个 miRNA 各自的贡献 —— 我若要用这个比值，必须自己补单变量对照</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8651,331 +8877,6 @@
       <c r="H10" s="6" t="inlineStr">
         <is>
           <t>最新机制约束</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="49" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>W9 · 落点器官：肠狭窄与心脏纤维化的真实病理</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>层级</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>PMID</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>期刊</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>为什么读</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>必须记下什么</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>[27720839](https://pubmed.ncbi.nlm.nih.gov/27720839/)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Gastroenterology</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Mechanisms, Management, and Treatment of Fibrosis in Patients With Inflammatory Bowel Diseases</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>IBD 纤维化的机制、管理与治疗（Gastroenterology 综述）——临床未满足需求的权威出处</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>狭窄的临床终点与发生率数字（写 Significance 用）；现有治疗为何无效</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>[39024569](https://pubmed.ncbi.nlm.nih.gov/39024569/)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>The Journal of clinical investigat</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>TWIST1+FAP+ fibroblasts in the pathogenesis of intestinal fibrosis in Crohn's disease</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>TWIST1+FAP+ 成纤维细胞在克罗恩病肠纤维化中的作用（JCI 2024）</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>病理性亚群的标记组合；他们如何从单细胞走到功能验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>[33119150](https://pubmed.ncbi.nlm.nih.gov/33119150/)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Scandinavian journal of immunology</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Mechanism of fibrosis and stricture formation in Crohn's disease</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>克罗恩病狭窄形成的机制</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>狭窄与炎症的可分离性</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>[42622514](https://pubmed.ncbi.nlm.nih.gov/42622514/)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Inflammatory bowel diseases</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026 年狭窄型克罗恩病的蛋白组学特征</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>可作为人源验证的分子标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>[29664017](https://pubmed.ncbi.nlm.nih.gov/29664017/)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>The Journal of clinical investigat</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Specialized fibroblast differentiated states underlie scar formation in the infarcted mouse heart</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>特化成纤维细胞状态决定瘢痕形成</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>成纤维细胞命运的分类框架</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>[39443792](https://pubmed.ncbi.nlm.nih.gov/39443792/)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Targeting immune-fibroblast cell communication in heart failure</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>靶向心衰中的免疫-成纤维细胞通讯（Nature 2024）</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>心脏侧的最新框架，用于我的 MYBPC3 线</t>
         </is>
       </c>
     </row>
@@ -9279,6 +9180,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>W9 · 落点器官：肠狭窄与心脏纤维化的真实病理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>为什么读</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>必须记下什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>[27720839](https://pubmed.ncbi.nlm.nih.gov/27720839/)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Gastroenterology</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Mechanisms, Management, and Treatment of Fibrosis in Patients With Inflammatory Bowel Diseases</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>IBD 纤维化的机制、管理与治疗（Gastroenterology 综述）——临床未满足需求的权威出处</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>狭窄的临床终点与发生率数字（写 Significance 用）；现有治疗为何无效</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>[39024569](https://pubmed.ncbi.nlm.nih.gov/39024569/)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>The Journal of clinical investigat</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>TWIST1+FAP+ fibroblasts in the pathogenesis of intestinal fibrosis in Crohn's disease</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>TWIST1+FAP+ 成纤维细胞在克罗恩病肠纤维化中的作用（JCI 2024）</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>病理性亚群的标记组合；他们如何从单细胞走到功能验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>[33119150](https://pubmed.ncbi.nlm.nih.gov/33119150/)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Scandinavian journal of immunology</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Mechanism of fibrosis and stricture formation in Crohn's disease</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>克罗恩病狭窄形成的机制</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>狭窄与炎症的可分离性</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>[39977234](https://pubmed.ncbi.nlm.nih.gov/39977234/)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Inflammatory bowel diseases</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Novel Transcriptomic Signatures in Fibrostenotic Crohn's Disease: Dysregulated Pathways, Promising Biomarkers</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>【替代】原 PMID 42622514（同刊 2026 蛋白质组）无开放全文，换成同刊同病同问题的转录组研究</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>①81 个重叠 DEG（64 上／17 下），GREM1、SERPINE1、LY96 为狭窄特异候选，GREM1 经 scRNA-seq（3 例、31,195 个细胞）定位于成纤维细胞；②设计上有配对内部对照（同一患者狭窄／近端／远端三点取材，RHI≤3 排除活动性炎症）并用公共数据集 GSE192786（19 纤维 vs 21 非纤维）外部验证；③但没有健康对照，无法区分「CD 特异」与「狭窄特异」；Fig.4 的功效分析基于合成数据而非真实前瞻队列；也无功能学验证 —— 这些基因目前只是关联标志，不能当已验证 biomarker 引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>[29664017](https://pubmed.ncbi.nlm.nih.gov/29664017/)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>The Journal of clinical investigat</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Specialized fibroblast differentiated states underlie scar formation in the infarcted mouse heart</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>特化成纤维细胞状态决定瘢痕形成</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>成纤维细胞命运的分类框架</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>[39443792](https://pubmed.ncbi.nlm.nih.gov/39443792/)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Targeting immune-fibroblast cell communication in heart failure</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>靶向心衰中的免疫-成纤维细胞通讯（Nature 2024）</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>心脏侧的最新框架，用于我的 MYBPC3 线</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9640,7 +9866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9965,7 +10191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10248,7 +10474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10529,7 +10755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11400,7 +11626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11683,7 +11909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11861,7 +12087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12113,7 +12339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12467,296 +12693,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>42622514, 39024569, 27720839</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>3 · 方向 3：乳酸/乳酰化 × 小 RNA 稳态</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>技术</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>用途</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>现状</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>关键参数</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>必须的对照</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>常见失败模式</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>依据</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>乳酸/糖酵解干预</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>建立代谢输入</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>✅（你的强项）</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>乳酸钠浓度〔FILL〕；糖酵解抑制剂〔FILL〕；时长〔FILL〕</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>pH 匹配对照 + 非代谢性酸化对照 —— 乳酸效应常被 pH 混淆</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>不做 pH 对照 → 结论直接被推翻</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>38653238</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>泛乳酰化 western 筛查</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>先看有没有</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>pan-Kla 抗体〔FILL 目录号〕</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>乳酸处理 vs 未处理；已报道的阳性底物（如 METTL3）作对照</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>泛抗体特异性有限 → 必须质谱确认</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>35320754, 37863889</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>AGO2/ZSWIM8/TUT4-7 免疫沉淀</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>富集候选底物</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>上样量〔FILL〕</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>IgG 对照</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>33853897</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>乳酰化位点质谱</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>定位修饰位点</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>🤝</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>富集策略〔FILL〕；最低上样量〔FILL〕；定位概率 &gt;0.75</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>未处理对照</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>化学乳酰化假阳性 → 需酶依赖性验证</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>35320754, 38653238</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>位点突变（K→R / K→Q）</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>功能验证</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>✅（碱基编辑）</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>内源位点敲入</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>未编辑同批；回补</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>赖氨酸位点常同时被乙酰化 → 需排除修饰竞争</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>38128537</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>酶学归因</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>是酶催化还是非酶化学反应</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>AARS1 敲低/抑制剂</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>AARS1 抑制剂已有（2026）</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>若为非酶反应，「通路」叙事不成立</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>38653238, 42744818</t>
+          <t>39977234, 39024569, 27720839</t>
         </is>
       </c>
     </row>
@@ -13072,6 +13009,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>3 · 方向 3：乳酸/乳酰化 × 小 RNA 稳态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>技术</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>现状</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>关键参数</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>必须的对照</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>常见失败模式</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>乳酸/糖酵解干预</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>建立代谢输入</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>✅（你的强项）</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>乳酸钠浓度〔FILL〕；糖酵解抑制剂〔FILL〕；时长〔FILL〕</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>pH 匹配对照 + 非代谢性酸化对照 —— 乳酸效应常被 pH 混淆</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>不做 pH 对照 → 结论直接被推翻</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>38653238</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>泛乳酰化 western 筛查</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>先看有没有</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>pan-Kla 抗体〔FILL 目录号〕</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>乳酸处理 vs 未处理；已报道的阳性底物（如 METTL3）作对照</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>泛抗体特异性有限 → 必须质谱确认</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>35320754, 37863889</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>AGO2/ZSWIM8/TUT4-7 免疫沉淀</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>富集候选底物</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>上样量〔FILL〕</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>IgG 对照</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>33853897</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>乳酰化位点质谱</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>定位修饰位点</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>🤝</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>富集策略〔FILL〕；最低上样量〔FILL〕；定位概率 &gt;0.75</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>未处理对照</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>化学乳酰化假阳性 → 需酶依赖性验证</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>35320754, 38653238</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>位点突变（K→R / K→Q）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>功能验证</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>✅（碱基编辑）</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>内源位点敲入</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>未编辑同批；回补</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>赖氨酸位点常同时被乙酰化 → 需排除修饰竞争</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>38128537</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>酶学归因</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>是酶催化还是非酶化学反应</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>AARS1 敲低/抑制剂</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>AARS1 抑制剂已有（2026）</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>若为非酶反应，「通路」叙事不成立</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>38653238, 42744818</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13318,7 +13544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13533,7 +13759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13670,7 +13896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14356,12 +14582,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14626,6 +14852,91 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>41542392</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2026 — TDMD 的 E3 机制：ZSWIM8 对 trigger 配对复合体偏好 up to 70 倍；加侧翼序列后共沉淀效率再升 100 倍（3 nM vs 300 nM）</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>方向 1 的定量尺度</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>41542532</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2026 — 线虫 EBAX-1（ZSWIM8 同源物）驱动 linker cell 非凋亡死亡（野生型 97% 降解，n=241）</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 归因约束：KO 表型 ≠ TDMD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>22095944</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>*JASN* 2012 — TGF-β1 抑制 miR-29：系膜细胞中 29a/b/c 分别降 28%／46%／37%；三个成员丰度差 5–14 倍（Fig.1F）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>方向 2 竞争解释 + 实验设计约束</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>39977234</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>*IBD* 2025 — 纤维狭窄型克罗恩转录组：81 个重叠 DEG（64 上/17 下），GREM1／SERPINE1／LY96 为狭窄特异候选，GREM1 经 scRNA-seq 定位于成纤维细胞</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>方向 2/4 的人源落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>41465114</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>*Genes* 2025 — 从代谢记忆到表观遗传记忆（替代 2010 年 Nat Rev Nephrol 版）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>方向 1 疾病概念（更新版）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
